--- a/seo/MasterLawn_Disavow.xlsx
+++ b/seo/MasterLawn_Disavow.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disavow (domain-level)'!$A$5:$G$893</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disavow (domain-level)'!$A$5:$G$1063</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G893"/>
+  <dimension ref="A1:G1063"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -31436,8 +31436,5558 @@
         </is>
       </c>
     </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>domain:blc-eu.com</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>blc-eu.com</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>2</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>109.105.49.240</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>cz</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); foreign-geo-cluster(cz); weak signal — human QA; QA agent → TOXIC (AS2, foreign CZ, generic name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>domain:blinks.monster</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>blinks.monster</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>2</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>104.21.9.211</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.monster); weak signal — human QA; QA agent → TOXIC (spam TLD .monster, link-farm name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>domain:blinks.sbs</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>blinks.sbs</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>4</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>104.21.3.70</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (spam-tld .sbs; nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>domain:blog-forest.help</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>blog-forest.help</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>0</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>104.21.38.56</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); spam-tld(.help); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .help, randomized name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>domain:booksreadr.org</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>booksreadr.org</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>4</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>92.249.46.138</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (off-topic books; India hosting cluster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>domain:horizon-layer.live</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>horizon-layer.live</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>2</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>16.60.178.120</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.live); weak signal — human QA; QA agent → TOXIC (spam TLD .live, nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>domain:kitabibrothers.com</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>kitabibrothers.com</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>2</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>147.93.17.109</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (India books site, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>domain:knows.monster</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>knows.monster</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>4</v>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>172.67.214.69</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); spam-tld(.monster); weak signal — human QA; QA agent → TOXIC (spam-tld .monster; nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>domain:knows.sbs</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>knows.sbs</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>2</v>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>172.67.183.150</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr"/>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (spam TLD .sbs, generic name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>domain:listglobe.com</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>listglobe.com</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>2</v>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>185.58.143.37</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); foreign-geo-cluster(se); weak signal — human QA; QA agent → TOXIC (listing directory farm, foreign SE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>domain:littlerocklawnlandscaping.com</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>littlerocklawnlandscaping.com</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>2</v>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>103.148.14.50</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>bd</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); foreign-geo-cluster(bd); weak signal — human QA; QA agent → TOXIC (lawn name but Bangladesh hosting, spam)</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>domain:marathiladies.com</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>marathiladies.com</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>2</v>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>92.249.46.138</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (India women's content, off-topic; shared farm IP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>domain:marketing-updatee.store</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>marketing-updatee.store</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>2</v>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>104.21.76.233</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.store); weak signal — human QA; QA agent → TOXIC (spam TLD .store, marketing farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>domain:nivira.shop</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>nivira.shop</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>2</v>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>104.21.73.168</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.shop); weak signal — human QA; QA agent → TOXIC (spam TLD .shop, generic name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>domain:plurio.shop</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>plurio.shop</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>2</v>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>104.21.79.128</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.shop); weak signal — human QA; QA agent → TOXIC (spam TLD .shop, generic name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>domain:raven-frost.online</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>raven-frost.online</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>0</v>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>172.67.213.220</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>domain:solace-moon.online</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>solace-moon.online</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>0</v>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>172.67.165.168</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>domain:sporstcenter.com</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>sporstcenter.com</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>2</v>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>92.249.46.138</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (typo domain, India, shared farm IP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>domain:subhikh.com</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>subhikh.com</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>3</v>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>93.188.2.55</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); foreign-geo-cluster(se); weak signal — human QA; QA agent → TOXIC (AS3 nonsense; foreign Sweden hosting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>domain:takes.homes</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>takes.homes</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>2</v>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>172.67.212.175</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.homes); weak signal — human QA; QA agent → TOXIC (spam TLD .homes, generic name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>domain:takes.sbs</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>takes.sbs</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>2</v>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>172.67.221.98</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr"/>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (spam TLD .sbs, generic name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>domain:tempest-ash.online</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>tempest-ash.online</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>0</v>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>104.21.91.165</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>domain:wants.cfd</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>wants.cfd</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>3</v>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>104.21.44.63</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); spam-tld(.cfd); weak signal — human QA; QA agent → TOXIC (spam-tld .cfd; nonsense low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>domain:xedulichdaklak.com</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>xedulichdaklak.com</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>2</v>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>103.74.121.46</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>vn</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); foreign-geo-cluster(vn); weak signal — human QA; QA agent → TOXIC (Vietnam travel, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>domain:xylo-mist.online</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>xylo-mist.online</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>0</v>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>104.21.8.93</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>domain:7minutos.es</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>7minutos.es</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>4</v>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>51.38.62.183</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (foreign Spanish news; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>domain:agroinsursas.com</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>agroinsursas.com</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>4</v>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>190.8.176.51</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (AS4 nonsense name; no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>domain:all-aged-domains.com</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>all-aged-domains.com</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>5</v>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>104.21.35.81</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (aged-domain reseller; PBN/link-scheme name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>domain:aloysionunes.com</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>aloysionunes.com</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>5</v>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>104.21.54.136</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (person name off-topic; AS5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>domain:animalstart.com</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>animalstart.com</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>4</v>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>172.67.209.131</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (off-topic animals content; AS4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>domain:answersmeta.com</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>answersmeta.com</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>2</v>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>104.21.17.21</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic Q&amp;A content-farm name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>domain:archive-hu.com</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>archive-hu.com</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>4</v>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>172.67.222.64</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (generic archive scraper; one-day link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>domain:associazioneagricoltorivalleverzasca.ch</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>associazioneagricoltorivalleverzasca.ch</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>3</v>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>128.65.195.34</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Swiss farming association, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>domain:ateliereleaurorei.ro</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>ateliereleaurorei.ro</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>2</v>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>172.67.203.169</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Romanian art site, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>domain:beepdreams.com</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>beepdreams.com</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>2</v>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>99.192.232.89</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>domain:betulcrime.com</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>betulcrime.com</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>4</v>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>172.67.192.162</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (AS4 nonsense name; irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>domain:blogerreviewers.com</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>blogerreviewers.com</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>2</v>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>172.67.215.250</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (review/blog farm name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>domain:bluecantera.com</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>bluecantera.com</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>2</v>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>192.169.172.129</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic name, no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>domain:capetownthing.co.za</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>capetownthing.co.za</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>3</v>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>69.163.180.195</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (South Africa site, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>domain:cityvetted.com</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>cityvetted.com</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>2</v>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>62.169.24.248</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC ('vetted' directory/review farm, foreign FR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>domain:civiltej.com</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>civiltej.com</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>3</v>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>108.181.242.144</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (AS3 nonsense name; no lawn relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>domain:cmocheatsheets.com</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>cmocheatsheets.com</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>2</v>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>104.21.91.99</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr"/>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Marketing content site, off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>domain:contractorsjunction.com</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>contractorsjunction.com</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>6</v>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>132.148.248.252</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (contractor directory farm; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>domain:corner-writers.blog</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>corner-writers.blog</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>2</v>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>104.21.84.108</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (article/writer farm, .blog TLD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>domain:coruzants.com</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>coruzants.com</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>2</v>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>172.67.192.96</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, nonsense name, single-day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>domain:cvillico.com</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>cvillico.com</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>2</v>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>104.21.14.64</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic name, no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>domain:daily-hacks.pages.dev</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>daily-hacks.pages.dev</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>2</v>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>172.66.44.243</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, content-farm name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>domain:decoratingmom.com</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>decoratingmom.com</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>2</v>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>172.67.201.81</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Interior-decor blog, off-topic, farm pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>domain:decoratingnerds.com</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>decoratingnerds.com</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>2</v>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>172.67.144.130</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr"/>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Interior-decor blog, off-topic, farm pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>domain:developmentmi.com</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>developmentmi.com</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>6</v>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>104.21.89.233</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr"/>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (generic name; no relevance AS6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>domain:divisionesmodularesjq.com</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>divisionesmodularesjq.com</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>6</v>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>162.215.210.151</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Spanish off-topic modular; irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>domain:domraider.eu.com</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>domraider.eu.com</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>0</v>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>172.67.212.236</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (AS0, generic domain-hack TLD, no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>domain:domraider.gb.net</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>domraider.gb.net</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>0</v>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>172.67.168.81</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (AS0, generic domain-hack TLD, no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>domain:domraider.it.com</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>domraider.it.com</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>0</v>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>104.21.1.165</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS0)</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (AS0, generic domain-hack TLD, no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>domain:dowjones.io</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>dowjones.io</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>6</v>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>192.0.66.208</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Dow Jones brand impersonation typo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>domain:echoz.pages.dev</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>echoz.pages.dev</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>2</v>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>172.66.47.143</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr"/>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>domain:entrepreneurscruise.com</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>entrepreneurscruise.com</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>2</v>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>104.21.31.149</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (business content farm, off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>domain:eurekster.com</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>eurekster.com</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>6</v>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>170.9.240.198</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (defunct brand; 122 sitewide irrelevant links)</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>domain:factmags.com</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>factmags.com</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>4</v>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>203.161.54.114</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (article magazine farm; shared IP with goooogla)</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>domain:fashionclothingnews.com</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>fashionclothingnews.com</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>2</v>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>172.67.156.33</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr"/>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (fashion news content farm, off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>domain:fastlifesite.com</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>fastlifesite.com</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>2</v>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>172.67.176.248</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr"/>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic content farm, single-day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>domain:findabusinessthat.com</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>findabusinessthat.com</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>5</v>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>172.67.146.82</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr"/>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (generic business directory farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>domain:findbiz.info</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>findbiz.info</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>2</v>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>185.139.128.92</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (business directory farm, .info)</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>domain:findingfarina.com</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>findingfarina.com</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>5</v>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>145.223.106.169</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (off-topic personal blog; AS5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>domain:findtor.com</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>findtor.com</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>2</v>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>3.132.208.69</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic name, no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>domain:fixhubs.net</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>fixhubs.net</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>2</v>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>172.67.139.28</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr"/>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic 'fix hub' template farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>domain:flamingos.pages.dev</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>flamingos.pages.dev</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>2</v>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>172.66.44.138</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr"/>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>domain:gardenshaper.com</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>gardenshaper.com</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>2</v>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>198.20.115.3</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>nl</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (garden-ish but foreign NL, generic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>domain:ggmap.co.com</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>ggmap.co.com</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>2</v>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>172.67.131.117</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr"/>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic domain-hack .co.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>domain:ggmap.us.com</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>ggmap.us.com</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>2</v>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>172.67.211.186</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr"/>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic domain-hack .us.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>domain:gladeflowers.com</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>gladeflowers.com</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>2</v>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>104.21.74.93</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr"/>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic, single-day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>domain:global-rank.pages.dev</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>global-rank.pages.dev</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>4</v>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>172.66.44.155</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr"/>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (SEO rank name; pages.dev throwaway host)</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>domain:global-ranks.pages.dev</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>global-ranks.pages.dev</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>4</v>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>172.66.44.110</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr"/>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (SEO rank name; pages.dev throwaway host)</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>domain:global-websites.pages.dev</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>global-websites.pages.dev</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>4</v>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>172.66.47.78</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr"/>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (SEO/directory name; pages.dev throwaway host)</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>domain:goooogla.com</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>goooogla.com</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>4</v>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>203.161.54.114</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Google typosquat; shared IP farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>domain:greattraveladvisor.com</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>greattraveladvisor.com</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>4</v>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>107.180.2.227</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (travel off-topic generic commercial name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>domain:harian24.com</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>harian24.com</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>2</v>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>104.21.65.94</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr"/>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Indonesian news, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>domain:hotonlinegaming.com</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>hotonlinegaming.com</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>3</v>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>172.67.129.112</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr"/>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (gambling/gaming off-topic high-risk vertical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>domain:huldra.pages.dev</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>huldra.pages.dev</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>2</v>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>172.66.44.118</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr"/>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>domain:isardomains.com</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>isardomains.com</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>3</v>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>104.21.48.247</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr"/>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (domain-reseller/directory name; link scheme signal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>domain:israelmilitaria.blogspot.com</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>israelmilitaria.blogspot.com</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>2</v>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>142.251.167.132</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (blogspot militaria, off-topic, 60 sitewide links)</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>domain:ivcfddhbsa.blogspot.com</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>ivcfddhbsa.blogspot.com</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>2</v>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>192.178.218.132</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (gibberish blogspot subdomain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>domain:jobsapp.info</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>jobsapp.info</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>6</v>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>172.67.128.71</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr"/>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (jobs off-topic; .info low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>domain:keirseybooks.com</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>keirseybooks.com</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>6</v>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>107.180.3.106</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (books off-topic; AS6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>domain:lawyerinjeddah.com</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>lawyerinjeddah.com</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>2</v>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>104.21.36.238</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr"/>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Jeddah lawyer, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>domain:libyanatravel.com</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>libyanatravel.com</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>2</v>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>104.21.70.241</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr"/>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Libya travel, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>domain:localbizsphere.com</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>localbizsphere.com</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>2</v>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>51.81.59.247</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (local business directory farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>domain:localbizzz.com</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>localbizzz.com</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>2</v>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>104.21.33.48</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr"/>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (local business directory farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>domain:lovetravellife.com</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>lovetravellife.com</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>4</v>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>108.181.247.75</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (travel off-topic; AS4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>domain:marketingupdatee.com</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>marketingupdatee.com</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>2</v>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>172.67.166.117</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr"/>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (marketing content farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>domain:masihnyata.com</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>masihnyata.com</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>2</v>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>172.67.149.19</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr"/>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Indonesian site, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>domain:mediaboooster.com</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>mediaboooster.com</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>5</v>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>104.21.14.45</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr"/>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (link/media-boost SEO service name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>domain:medidocs.com</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>medidocs.com</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>4</v>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>72.167.102.111</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (medical off-topic; AS4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>domain:mygirlyspace.com</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>mygirlyspace.com</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>3</v>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>31.170.166.36</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (off-topic lifestyle; AS3 low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>domain:mymarketpost.com</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>mymarketpost.com</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>2</v>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>172.67.159.15</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr"/>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (PR/market post content farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>domain:naturalegno.net</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>naturalegno.net</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>2</v>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>104.21.93.87</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr"/>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Italian wood site, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>domain:newsblogsports.site</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>newsblogsports.site</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>2</v>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>172.67.220.122</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr"/>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (spam TLD .site, news/sports farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>domain:obake.pages.dev</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>obake.pages.dev</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>2</v>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>172.66.44.72</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr"/>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>domain:onlinelocalbrand.com</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>onlinelocalbrand.com</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>2</v>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>185.163.16.3</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (marketing/branding farm name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>domain:onlineshoppingidea.com</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>onlineshoppingidea.com</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>2</v>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>104.21.20.72</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr"/>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (shopping content farm, off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>domain:phanerosart.com</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>phanerosart.com</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>2</v>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>104.21.56.40</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr"/>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (art site, off-topic, single-day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>domain:pingeras.blogspot.com</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>pingeras.blogspot.com</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>2</v>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>142.251.163.132</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (blogspot, generic, 14 links)</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>domain:plrdownloadshub.com</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>plrdownloadshub.com</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>2</v>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>172.67.166.90</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr"/>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (PLR downloads, spam vertical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>domain:plumeriamarketing.com</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>plumeriamarketing.com</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>2</v>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>104.21.15.10</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr"/>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (marketing agency, off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>domain:popularask.net</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>popularask.net</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>6</v>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>104.21.23.20</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr"/>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Q&amp;A article farm; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>domain:poshcoloringstudiostorer.blogspot.com</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>poshcoloringstudiostorer.blogspot.com</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>2</v>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>142.251.167.132</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (blogspot, off-topic coloring, odd name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>domain:quotesblom.com</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>quotesblom.com</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>104.21.14.53</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr"/>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (quotes content farm, single-day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>domain:realtalkaj.me</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>realtalkaj.me</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>192.0.78.25</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic personal .me blog)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>domain:revan-me.com</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>revan-me.com</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>160.153.129.19</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (AS3 randomized nonsense name; irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>domain:reviewmx.com</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>reviewmx.com</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>172.67.164.204</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr"/>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (review farm name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>domain:robuta.com</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>robuta.com</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>162.159.140.164</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (brandable nonsense; no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>domain:royaldb.us.com</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>royaldb.us.com</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>104.21.87.48</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr"/>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic .us.com, single-day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>domain:rumoursnews.com</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>rumoursnews.com</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>217.196.54.177</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (gossip news content farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>domain:shoplogist.com</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>shoplogist.com</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>172.67.180.152</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr"/>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic shop/logistics name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>domain:sisgroup.lk</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>sisgroup.lk</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>194.233.75.17</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>sg</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>qa-override:foreign-geo-cluster(sg)</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>foreign-geo-cluster(sg); weak signal — human QA; QA agent → TOXIC (Sri Lanka foreign cluster; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>domain:slapshady.com</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>slapshady.com</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>208.109.22.214</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (AS4 nonsense name; irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>domain:sportsbikeparts.pk</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>sportsbikeparts.pk</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>172.67.167.23</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr"/>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Pakistan bike parts, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>domain:starcourts.com</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>starcourts.com</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>104.21.68.102</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr"/>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (generic nonsense name; no relevance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>domain:startupwebsolutions.com.au</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>startupwebsolutions.com.au</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>172.67.138.213</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr"/>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (generic SEO/web-agency name; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>domain:studartcorrea.com.br</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>studartcorrea.com.br</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>172.67.196.110</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr"/>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Brazil art studio, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>domain:tapalmbeaches.com</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>tapalmbeaches.com</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>104.18.20.240</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr"/>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (off-topic location site, generic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>domain:techsb.ca</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>techsb.ca</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>35.212.103.243</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic tech name, off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>domain:theambiencenews.com</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>theambiencenews.com</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>198.12.232.179</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (news article farm; one-day link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>domain:thecloudherald.com</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>thecloudherald.com</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>172.66.47.22</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr"/>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic news content farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>domain:thehomefixhub.com</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>thehomefixhub.com</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>172.67.142.210</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr"/>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC ('home fix hub' template farm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>domain:themicrodigits.com</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>themicrodigits.com</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>104.21.71.254</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr"/>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic tech, single-day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>domain:thetarotalk.com</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>thetarotalk.com</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>172.67.166.149</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr"/>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (tarot site, off-topic vertical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>domain:turkiyelinux.com</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>turkiyelinux.com</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>46.20.34.203</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Turkey linux site, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>domain:ultimatelistzone.com</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>ultimatelistzone.com</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>167.114.32.229</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (listing/list-zone farm name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>domain:unanswered.io</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>unanswered.io</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>104.21.73.181</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr"/>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (generic Q&amp;A; off-topic low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>domain:updatejakarta.com</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>updatejakarta.com</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>104.21.34.221</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr"/>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (foreign Jakarta news; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>domain:usapridenetwork.us</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>usapridenetwork.us</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>172.67.179.136</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr"/>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS6)</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (generic network name; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>domain:webbys.pages.dev</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>webbys.pages.dev</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>172.66.47.196</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr"/>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (pages.dev throwaway; generic name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>domain:webhubsites.com</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>webhubsites.com</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>172.67.192.40</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr"/>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (web-hub/directory name; link-scheme signal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>domain:wecelebrities.com</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>wecelebrities.com</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>172.67.199.73</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr"/>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (celebrity gossip off-topic; AS3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>domain:weedspots.net</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>weedspots.net</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>165.227.88.129</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS4)</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (likely cannabis directory; off-topic risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>domain:willettonuniforms.com.au</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>willettonuniforms.com.au</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>104.21.48.84</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr"/>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Australia uniforms shop, off-topic foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>domain:worldlinksites.com</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>worldlinksites.com</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>104.21.11.111</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr"/>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS5)</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (link-farm/directory name; link scheme)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>domain:writfy.com</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>writfy.com</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>104.21.57.78</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr"/>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS3)</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (AS3 nonsense/writing-mill name; irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>domain:yeow.ai</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>yeow.ai</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>157.230.165.86</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>qa-override:very-low-authority(AS2)</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic .ai site, off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>domain:addresspage.com</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>addresspage.com</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>172.67.151.92</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr"/>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (address listing directory; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>domain:buyatreechangealife.com</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>buyatreechangealife.com</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>198.185.159.144</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Aus lifestyle off-topic; irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>domain:designedbyai.io</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>designedbyai.io</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>104.21.34.193</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr"/>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (AI design tool off-topic; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>domain:dreamchaserhub.com</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>dreamchaserhub.com</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>205.196.220.15</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (generic hub off-topic; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>domain:ejobscircular.com</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>ejobscircular.com</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>104.21.68.155</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr"/>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Bangladesh jobs off-topic; foreign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>domain:escuela-indecopi.edu.pe</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>escuela-indecopi.edu.pe</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>173.212.231.25</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Peru edu hosted France; suspicious irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>domain:gorentals.com.pa</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>gorentals.com.pa</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>89.17.204.80</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Panama rentals foreign; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>domain:greentechtree.com</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>greentechtree.com</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>174.136.57.104</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (generic green-tech; off-topic low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>domain:intently.co</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>intently.co</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>67.227.198.170</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (generic off-topic; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>domain:linkcenter.com</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>linkcenter.com</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>78.129.199.5</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (link-farm/directory name; link scheme)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>domain:loginslink.com</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>loginslink.com</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>104.26.12.144</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr"/>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>qa-override:known-good</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>recognized legitimate platform (neutral-authority); QA agent → TOXIC (Auto-generated login-link scraper; off-topic SEO spam)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>domain:mygreenbucks.net</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>mygreenbucks.net</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>32</v>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>104.21.39.229</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr"/>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>qa-override:authority-no-spam</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>AS&gt;=20 with no spam signal; QA agent → TOXIC (GPT/survey site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>domain:olivare.com.ar</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>olivare.com.ar</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>104.21.40.229</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Argentina one-day link; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>domain:openingtimes.co</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>openingtimes.co</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>194.26.222.202</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (business-hours directory aggregator; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>domain:pixwox.org</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>pixwox.org</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>162.0.235.107</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Instagram scraper site; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>domain:reputablebusinesses.com</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>reputablebusinesses.com</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>145.223.126.72</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (business directory farm; one-day link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>domain:resonancelabjo.com</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>resonancelabjo.com</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>160.153.133.225</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Jordan off-topic lab; irrelevant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>domain:semalt.ai</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>semalt.ai</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>185.100.234.251</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>nl</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (notorious spam/SEO referrer brand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>domain:sergechel.info</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>sergechel.info</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>104.21.31.88</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr"/>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (personal .info off-topic; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>domain:solvermatic.com</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>solvermatic.com</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>162.159.134.42</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (generic off-topic; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>domain:southernlanka.lk</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>southernlanka.lk</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>135.181.210.47</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>fi</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Sri Lanka foreign; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>domain:southfwb.com</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>southfwb.com</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>104.21.16.20</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr"/>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (generic name; one-day low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>domain:sportmediaset.co</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>sportmediaset.co</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>172.67.192.199</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr"/>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Mediaset sport typo; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>domain:swipenow.com</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>swipenow.com</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>148.72.27.147</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (generic app off-topic; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>domain:thenllc.ca</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>thenllc.ca</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>156.67.77.68</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (generic LLC Canada; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>domain:thesocialhouseja.com</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>thesocialhouseja.com</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>72.167.69.37</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (Jamaica social off-topic; low authority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>domain:vangvela.com</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>vangvela.com</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>195.35.60.128</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (nonsense name off-topic; AS16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>domain:viral-status.com</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>viral-status.com</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>104.21.72.65</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr"/>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (viral-content farm; off-topic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>domain:wealthyoverview.com</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>wealthyoverview.com</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>172.67.130.236</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr"/>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (finance off-topic content; AS7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>domain:websitescrawl.com</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>websitescrawl.com</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>68.178.235.175</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>qa-override:unclassified</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>no strong signal — human QA; QA agent → TOXIC (crawler/directory SEO name; link scheme)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:G893"/>
+  <autoFilter ref="A5:G1063"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/seo/MasterLawn_Disavow.xlsx
+++ b/seo/MasterLawn_Disavow.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disavow (domain-level)'!$A$5:$G$1063</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disavow (domain-level)'!$A$5:$G$1009</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1063"/>
+  <dimension ref="A1:G1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -31303,43 +31303,47 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>domain:landscape.directory</t>
+          <t>domain:likesite.org</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>landscape.directory</t>
+          <t>likesite.org</t>
         </is>
       </c>
       <c r="C890" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>104.21.51.74</t>
-        </is>
-      </c>
-      <c r="E890" t="inlineStr"/>
+          <t>64.182.251.5</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>directory/article/bookmark-spam-name</t>
+          <t>pbn-ip-cluster:64.182.251</t>
         </is>
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>directory/article/bookmark-spam-name</t>
+          <t>pbn-ip-cluster:64.182.251</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>domain:likesite.org</t>
+          <t>domain:safebizlistings.com</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>likesite.org</t>
+          <t>safebizlistings.com</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -31347,7 +31351,7 @@
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>64.182.251.5</t>
+          <t>18.117.203.238</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -31357,32 +31361,32 @@
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>pbn-ip-cluster:64.182.251</t>
+          <t>directory/article/bookmark-spam-name</t>
         </is>
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>pbn-ip-cluster:64.182.251</t>
+          <t>directory/article/bookmark-spam-name</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>domain:safebizlistings.com</t>
+          <t>domain:websnoop.org</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>safebizlistings.com</t>
+          <t>websnoop.org</t>
         </is>
       </c>
       <c r="C892" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>18.117.203.238</t>
+          <t>69.13.111.202</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -31392,59 +31396,59 @@
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>directory/article/bookmark-spam-name</t>
+          <t>pbn-ip-cluster:69.13.111</t>
         </is>
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>directory/article/bookmark-spam-name</t>
+          <t>pbn-ip-cluster:69.13.111</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>domain:websnoop.org</t>
+          <t>domain:blc-eu.com</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>websnoop.org</t>
+          <t>blc-eu.com</t>
         </is>
       </c>
       <c r="C893" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>69.13.111.202</t>
+          <t>109.105.49.240</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>cz</t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>pbn-ip-cluster:69.13.111</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>pbn-ip-cluster:69.13.111</t>
+          <t>very-low-authority(AS2); foreign-geo-cluster(cz); weak signal — human QA; QA agent → TOXIC (foreign generic no relevance)</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>domain:blc-eu.com</t>
+          <t>domain:blinks.monster</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>blc-eu.com</t>
+          <t>blinks.monster</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -31452,14 +31456,10 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>109.105.49.240</t>
-        </is>
-      </c>
-      <c r="E894" t="inlineStr">
-        <is>
-          <t>cz</t>
-        </is>
-      </c>
+          <t>104.21.9.211</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr"/>
       <c r="F894" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -31467,147 +31467,151 @@
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); foreign-geo-cluster(cz); weak signal — human QA; QA agent → TOXIC (AS2, foreign CZ, generic name)</t>
+          <t>very-low-authority(AS2); spam-tld(.monster); weak signal — human QA; QA agent → TOXIC (Spam TLD)</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>domain:blinks.monster</t>
+          <t>domain:blinks.sbs</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>blinks.monster</t>
+          <t>blinks.sbs</t>
         </is>
       </c>
       <c r="C895" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>104.21.9.211</t>
+          <t>104.21.3.70</t>
         </is>
       </c>
       <c r="E895" t="inlineStr"/>
       <c r="F895" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.monster); weak signal — human QA; QA agent → TOXIC (spam TLD .monster, link-farm name)</t>
+          <t>very-low-authority(AS4); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (Backlink spam)</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>domain:blinks.sbs</t>
+          <t>domain:blog-forest.help</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>blinks.sbs</t>
+          <t>blog-forest.help</t>
         </is>
       </c>
       <c r="C896" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>104.21.3.70</t>
+          <t>104.21.38.56</t>
         </is>
       </c>
       <c r="E896" t="inlineStr"/>
       <c r="F896" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (spam-tld .sbs; nonsense name)</t>
+          <t>very-low-authority(AS0); spam-tld(.help); weak signal — human QA; QA agent → TOXIC (spam tld zero authority)</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>domain:blog-forest.help</t>
+          <t>domain:booksreadr.org</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>blog-forest.help</t>
+          <t>booksreadr.org</t>
         </is>
       </c>
       <c r="C897" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>104.21.38.56</t>
-        </is>
-      </c>
-      <c r="E897" t="inlineStr"/>
+          <t>92.249.46.138</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); spam-tld(.help); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .help, randomized name)</t>
+          <t>very-low-authority(AS4); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (Aged domain sold for backlinks; PBN IP)</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>domain:booksreadr.org</t>
+          <t>domain:horizon-layer.live</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>booksreadr.org</t>
+          <t>horizon-layer.live</t>
         </is>
       </c>
       <c r="C898" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>92.249.46.138</t>
+          <t>16.60.178.120</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>gb</t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (off-topic books; India hosting cluster)</t>
+          <t>very-low-authority(AS2); spam-tld(.live); weak signal — human QA; QA agent → TOXIC (Spam TLD generic nonsense name)</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>domain:horizon-layer.live</t>
+          <t>domain:kitabibrothers.com</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>horizon-layer.live</t>
+          <t>kitabibrothers.com</t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -31615,12 +31619,12 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>16.60.178.120</t>
+          <t>147.93.17.109</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>gb</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
@@ -31630,85 +31634,81 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.live); weak signal — human QA; QA agent → TOXIC (spam TLD .live, nonsense name)</t>
+          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (foreign irrelevant low authority)</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>domain:kitabibrothers.com</t>
+          <t>domain:knows.monster</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>kitabibrothers.com</t>
+          <t>knows.monster</t>
         </is>
       </c>
       <c r="C900" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>147.93.17.109</t>
-        </is>
-      </c>
-      <c r="E900" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+          <t>172.67.214.69</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr"/>
       <c r="F900" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (India books site, off-topic foreign)</t>
+          <t>very-low-authority(AS4); spam-tld(.monster); weak signal — human QA; QA agent → TOXIC (Spam TLD; low authority)</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>domain:knows.monster</t>
+          <t>domain:knows.sbs</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>knows.monster</t>
+          <t>knows.sbs</t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>172.67.214.69</t>
+          <t>172.67.183.150</t>
         </is>
       </c>
       <c r="E901" t="inlineStr"/>
       <c r="F901" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); spam-tld(.monster); weak signal — human QA; QA agent → TOXIC (spam-tld .monster; nonsense name)</t>
+          <t>very-low-authority(AS2); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (Spam TLD throwaway host)</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>domain:knows.sbs</t>
+          <t>domain:listglobe.com</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>knows.sbs</t>
+          <t>listglobe.com</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -31716,10 +31716,14 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>172.67.183.150</t>
-        </is>
-      </c>
-      <c r="E902" t="inlineStr"/>
+          <t>185.58.143.37</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
       <c r="F902" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -31727,19 +31731,19 @@
       </c>
       <c r="G902" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (spam TLD .sbs, generic name)</t>
+          <t>very-low-authority(AS2); foreign-geo-cluster(se); weak signal — human QA; QA agent → TOXIC (Foreign listing directory low authority)</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>domain:listglobe.com</t>
+          <t>domain:marathiladies.com</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>listglobe.com</t>
+          <t>marathiladies.com</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -31747,12 +31751,12 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>185.58.143.37</t>
+          <t>92.249.46.138</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>in</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
@@ -31762,19 +31766,19 @@
       </c>
       <c r="G903" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); foreign-geo-cluster(se); weak signal — human QA; QA agent → TOXIC (listing directory farm, foreign SE)</t>
+          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (foreign content ip cluster)</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>domain:littlerocklawnlandscaping.com</t>
+          <t>domain:marketing-updatee.store</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>littlerocklawnlandscaping.com</t>
+          <t>marketing-updatee.store</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -31782,14 +31786,10 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>103.148.14.50</t>
-        </is>
-      </c>
-      <c r="E904" t="inlineStr">
-        <is>
-          <t>bd</t>
-        </is>
-      </c>
+          <t>104.21.76.233</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr"/>
       <c r="F904" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -31797,19 +31797,19 @@
       </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); foreign-geo-cluster(bd); weak signal — human QA; QA agent → TOXIC (lawn name but Bangladesh hosting, spam)</t>
+          <t>very-low-authority(AS2); spam-tld(.store); weak signal — human QA; QA agent → TOXIC (Spam TLD misspelled throwaway name)</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>domain:marathiladies.com</t>
+          <t>domain:nivira.shop</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>marathiladies.com</t>
+          <t>nivira.shop</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -31817,14 +31817,10 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>92.249.46.138</t>
-        </is>
-      </c>
-      <c r="E905" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+          <t>104.21.73.168</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr"/>
       <c r="F905" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -31832,19 +31828,19 @@
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (India women's content, off-topic; shared farm IP)</t>
+          <t>very-low-authority(AS2); spam-tld(.shop); weak signal — human QA; QA agent → TOXIC (Spam TLD)</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>domain:marketing-updatee.store</t>
+          <t>domain:plurio.shop</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>marketing-updatee.store</t>
+          <t>plurio.shop</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -31852,7 +31848,7 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>104.21.76.233</t>
+          <t>104.21.79.128</t>
         </is>
       </c>
       <c r="E906" t="inlineStr"/>
@@ -31863,143 +31859,147 @@
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.store); weak signal — human QA; QA agent → TOXIC (spam TLD .store, marketing farm)</t>
+          <t>very-low-authority(AS2); spam-tld(.shop); weak signal — human QA; QA agent → TOXIC (Spam TLD)</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>domain:nivira.shop</t>
+          <t>domain:raven-frost.online</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>nivira.shop</t>
+          <t>raven-frost.online</t>
         </is>
       </c>
       <c r="C907" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>104.21.73.168</t>
+          <t>172.67.213.220</t>
         </is>
       </c>
       <c r="E907" t="inlineStr"/>
       <c r="F907" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.shop); weak signal — human QA; QA agent → TOXIC (spam TLD .shop, generic name)</t>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (Spam TLD)</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>domain:plurio.shop</t>
+          <t>domain:solace-moon.online</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>plurio.shop</t>
+          <t>solace-moon.online</t>
         </is>
       </c>
       <c r="C908" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>104.21.79.128</t>
+          <t>172.67.165.168</t>
         </is>
       </c>
       <c r="E908" t="inlineStr"/>
       <c r="F908" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G908" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.shop); weak signal — human QA; QA agent → TOXIC (spam TLD .shop, generic name)</t>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (Random name spam .online TLD)</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>domain:raven-frost.online</t>
+          <t>domain:sporstcenter.com</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>raven-frost.online</t>
+          <t>sporstcenter.com</t>
         </is>
       </c>
       <c r="C909" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>172.67.213.220</t>
-        </is>
-      </c>
-      <c r="E909" t="inlineStr"/>
+          <t>92.249.46.138</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (Typosquat sportscenter; PBN IP)</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>domain:solace-moon.online</t>
+          <t>domain:takes.homes</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>solace-moon.online</t>
+          <t>takes.homes</t>
         </is>
       </c>
       <c r="C910" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>172.67.165.168</t>
+          <t>172.67.212.175</t>
         </is>
       </c>
       <c r="E910" t="inlineStr"/>
       <c r="F910" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+          <t>very-low-authority(AS2); spam-tld(.homes); weak signal — human QA; QA agent → TOXIC (spam tld throwaway host)</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>domain:sporstcenter.com</t>
+          <t>domain:takes.sbs</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>sporstcenter.com</t>
+          <t>takes.sbs</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -32007,14 +32007,10 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>92.249.46.138</t>
-        </is>
-      </c>
-      <c r="E911" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+          <t>172.67.221.98</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr"/>
       <c r="F911" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -32022,279 +32018,275 @@
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); foreign-geo-cluster(in); weak signal — human QA; QA agent → TOXIC (typo domain, India, shared farm IP)</t>
+          <t>very-low-authority(AS2); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (spam tld throwaway host)</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>domain:subhikh.com</t>
+          <t>domain:tempest-ash.online</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>subhikh.com</t>
+          <t>tempest-ash.online</t>
         </is>
       </c>
       <c r="C912" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>93.188.2.55</t>
-        </is>
-      </c>
-      <c r="E912" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
+          <t>104.21.91.165</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr"/>
       <c r="F912" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); foreign-geo-cluster(se); weak signal — human QA; QA agent → TOXIC (AS3 nonsense; foreign Sweden hosting)</t>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (Random name spam .online TLD)</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>domain:takes.homes</t>
+          <t>domain:wants.cfd</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>takes.homes</t>
+          <t>wants.cfd</t>
         </is>
       </c>
       <c r="C913" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>172.67.212.175</t>
+          <t>104.21.44.63</t>
         </is>
       </c>
       <c r="E913" t="inlineStr"/>
       <c r="F913" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.homes); weak signal — human QA; QA agent → TOXIC (spam TLD .homes, generic name)</t>
+          <t>very-low-authority(AS3); spam-tld(.cfd); weak signal — human QA; QA agent → TOXIC (Spam TLD; generic)</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>domain:takes.sbs</t>
+          <t>domain:xylo-mist.online</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>takes.sbs</t>
+          <t>xylo-mist.online</t>
         </is>
       </c>
       <c r="C914" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>172.67.221.98</t>
+          <t>104.21.8.93</t>
         </is>
       </c>
       <c r="E914" t="inlineStr"/>
       <c r="F914" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); spam-tld(.sbs); weak signal — human QA; QA agent → TOXIC (spam TLD .sbs, generic name)</t>
+          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (Nonsense name spam TLD zero authority)</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>domain:tempest-ash.online</t>
+          <t>domain:7minutos.es</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>tempest-ash.online</t>
+          <t>7minutos.es</t>
         </is>
       </c>
       <c r="C915" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>104.21.91.165</t>
-        </is>
-      </c>
-      <c r="E915" t="inlineStr"/>
+          <t>51.38.62.183</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (foreign site no relevance)</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>domain:wants.cfd</t>
+          <t>domain:agroinsursas.com</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>wants.cfd</t>
+          <t>agroinsursas.com</t>
         </is>
       </c>
       <c r="C916" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>104.21.44.63</t>
-        </is>
-      </c>
-      <c r="E916" t="inlineStr"/>
+          <t>190.8.176.51</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); spam-tld(.cfd); weak signal — human QA; QA agent → TOXIC (spam-tld .cfd; nonsense low authority)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Foreign site serving casino spam pages)</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>domain:xedulichdaklak.com</t>
+          <t>domain:all-aged-domains.com</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>xedulichdaklak.com</t>
+          <t>all-aged-domains.com</t>
         </is>
       </c>
       <c r="C917" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>103.74.121.46</t>
-        </is>
-      </c>
-      <c r="E917" t="inlineStr">
-        <is>
-          <t>vn</t>
-        </is>
-      </c>
+          <t>104.21.35.81</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr"/>
       <c r="F917" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS5)</t>
         </is>
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); foreign-geo-cluster(vn); weak signal — human QA; QA agent → TOXIC (Vietnam travel, off-topic foreign)</t>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (Aged-domain seller; SEO spam)</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>domain:xylo-mist.online</t>
+          <t>domain:aloysionunes.com</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>xylo-mist.online</t>
+          <t>aloysionunes.com</t>
         </is>
       </c>
       <c r="C918" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>104.21.8.93</t>
+          <t>104.21.54.136</t>
         </is>
       </c>
       <c r="E918" t="inlineStr"/>
       <c r="F918" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS5)</t>
         </is>
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); spam-tld(.online); weak signal — human QA; QA agent → TOXIC (AS0, spam TLD .online, randomized nonsense name)</t>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (foreign personal site irrelevant)</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>domain:7minutos.es</t>
+          <t>domain:answersmeta.com</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>7minutos.es</t>
+          <t>answersmeta.com</t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>51.38.62.183</t>
-        </is>
-      </c>
-      <c r="E919" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
+          <t>104.21.17.21</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr"/>
       <c r="F919" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (foreign Spanish news; off-topic)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic Q&amp;A low authority)</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>domain:agroinsursas.com</t>
+          <t>domain:archive-hu.com</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>agroinsursas.com</t>
+          <t>archive-hu.com</t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -32302,14 +32294,10 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>190.8.176.51</t>
-        </is>
-      </c>
-      <c r="E920" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.222.64</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr"/>
       <c r="F920" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS4)</t>
@@ -32317,81 +32305,89 @@
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (AS4 nonsense name; no relevance)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Generic)</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>domain:all-aged-domains.com</t>
+          <t>domain:beepdreams.com</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>all-aged-domains.com</t>
+          <t>beepdreams.com</t>
         </is>
       </c>
       <c r="C921" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>104.21.35.81</t>
-        </is>
-      </c>
-      <c r="E921" t="inlineStr"/>
+          <t>99.192.232.89</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS5)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (aged-domain reseller; PBN/link-scheme name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Random brand; very low authority)</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>domain:aloysionunes.com</t>
+          <t>domain:besttownfencepros.com</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>aloysionunes.com</t>
+          <t>besttownfencepros.com</t>
         </is>
       </c>
       <c r="C922" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>104.21.54.136</t>
-        </is>
-      </c>
-      <c r="E922" t="inlineStr"/>
+          <t>34.174.136.8</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS5)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (person name off-topic; AS5)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Auto-generated fence-contractor listing directory; scraper spam)</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>domain:animalstart.com</t>
+          <t>domain:betulcrime.com</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>animalstart.com</t>
+          <t>betulcrime.com</t>
         </is>
       </c>
       <c r="C923" t="n">
@@ -32399,7 +32395,7 @@
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>172.67.209.131</t>
+          <t>172.67.192.162</t>
         </is>
       </c>
       <c r="E923" t="inlineStr"/>
@@ -32410,19 +32406,19 @@
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (off-topic animals content; AS4)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (foreign irrelevant ip cluster)</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>domain:answersmeta.com</t>
+          <t>domain:blogerreviewers.com</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>answersmeta.com</t>
+          <t>blogerreviewers.com</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -32430,7 +32426,7 @@
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>104.21.17.21</t>
+          <t>172.67.215.250</t>
         </is>
       </c>
       <c r="E924" t="inlineStr"/>
@@ -32441,50 +32437,54 @@
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic Q&amp;A content-farm name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Review-spam name)</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>domain:archive-hu.com</t>
+          <t>domain:bluecantera.com</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>archive-hu.com</t>
+          <t>bluecantera.com</t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>172.67.222.64</t>
-        </is>
-      </c>
-      <c r="E925" t="inlineStr"/>
+          <t>192.169.172.129</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (generic archive scraper; one-day link)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Real firm site hijacked with casino spam)</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>domain:associazioneagricoltorivalleverzasca.ch</t>
+          <t>domain:capetownthing.co.za</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>associazioneagricoltorivalleverzasca.ch</t>
+          <t>capetownthing.co.za</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -32492,12 +32492,12 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>128.65.195.34</t>
+          <t>69.163.180.195</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>ch</t>
+          <t>us</t>
         </is>
       </c>
       <c r="F926" t="inlineStr">
@@ -32507,19 +32507,19 @@
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Swiss farming association, off-topic foreign)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Foreign South Africa site; no relevance)</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>domain:ateliereleaurorei.ro</t>
+          <t>domain:cityvetted.com</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>ateliereleaurorei.ro</t>
+          <t>cityvetted.com</t>
         </is>
       </c>
       <c r="C927" t="n">
@@ -32527,10 +32527,14 @@
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>172.67.203.169</t>
-        </is>
-      </c>
-      <c r="E927" t="inlineStr"/>
+          <t>62.169.24.248</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
       <c r="F927" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -32538,27 +32542,27 @@
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Romanian art site, off-topic foreign)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic directory-style)</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>domain:beepdreams.com</t>
+          <t>domain:civiltej.com</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>beepdreams.com</t>
+          <t>civiltej.com</t>
         </is>
       </c>
       <c r="C928" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>99.192.232.89</t>
+          <t>108.181.242.144</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -32568,55 +32572,55 @@
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic nonsense name)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Low-authority)</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>domain:betulcrime.com</t>
+          <t>domain:cmocheatsheets.com</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>betulcrime.com</t>
+          <t>cmocheatsheets.com</t>
         </is>
       </c>
       <c r="C929" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>172.67.192.162</t>
+          <t>104.21.91.99</t>
         </is>
       </c>
       <c r="E929" t="inlineStr"/>
       <c r="F929" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (AS4 nonsense name; irrelevant)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Shared-IP cluster)</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>domain:blogerreviewers.com</t>
+          <t>domain:corner-writers.blog</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>blogerreviewers.com</t>
+          <t>corner-writers.blog</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -32624,7 +32628,7 @@
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>172.67.215.250</t>
+          <t>104.21.84.108</t>
         </is>
       </c>
       <c r="E930" t="inlineStr"/>
@@ -32635,19 +32639,19 @@
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (review/blog farm name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Guest-post/writing content farm)</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>domain:bluecantera.com</t>
+          <t>domain:coruzants.com</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>bluecantera.com</t>
+          <t>coruzants.com</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -32655,14 +32659,10 @@
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>192.169.172.129</t>
-        </is>
-      </c>
-      <c r="E931" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.192.96</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr"/>
       <c r="F931" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -32670,54 +32670,50 @@
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic name, no relevance)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Copycat of paid-PR media platform)</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>domain:capetownthing.co.za</t>
+          <t>domain:cvillico.com</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>capetownthing.co.za</t>
+          <t>cvillico.com</t>
         </is>
       </c>
       <c r="C932" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>69.163.180.195</t>
-        </is>
-      </c>
-      <c r="E932" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.14.64</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr"/>
       <c r="F932" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (South Africa site, off-topic foreign)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic)</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>domain:cityvetted.com</t>
+          <t>domain:daily-hacks.pages.dev</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>cityvetted.com</t>
+          <t>daily-hacks.pages.dev</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -32725,14 +32721,10 @@
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>62.169.24.248</t>
-        </is>
-      </c>
-      <c r="E933" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
+          <t>172.66.44.243</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr"/>
       <c r="F933" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -32740,182 +32732,178 @@
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC ('vetted' directory/review farm, foreign FR)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev host)</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>domain:civiltej.com</t>
+          <t>domain:developmentmi.com</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>civiltej.com</t>
+          <t>developmentmi.com</t>
         </is>
       </c>
       <c r="C934" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>108.181.242.144</t>
-        </is>
-      </c>
-      <c r="E934" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.89.233</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr"/>
       <c r="F934" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:very-low-authority(AS6)</t>
         </is>
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (AS3 nonsense name; no lawn relevance)</t>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Article-directory WordPress theme; article spam)</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>domain:cmocheatsheets.com</t>
+          <t>domain:divisionesmodularesjq.com</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>cmocheatsheets.com</t>
+          <t>divisionesmodularesjq.com</t>
         </is>
       </c>
       <c r="C935" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>104.21.91.99</t>
-        </is>
-      </c>
-      <c r="E935" t="inlineStr"/>
+          <t>162.215.210.151</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS6)</t>
         </is>
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Marketing content site, off-topic)</t>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Spanish modular-furniture irrelevant foreign site)</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>domain:contractorsjunction.com</t>
+          <t>domain:domraider.eu.com</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>contractorsjunction.com</t>
+          <t>domraider.eu.com</t>
         </is>
       </c>
       <c r="C936" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>132.148.248.252</t>
-        </is>
-      </c>
-      <c r="E936" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.212.236</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr"/>
       <c r="F936" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (contractor directory farm; low authority)</t>
+          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (Domain-related)</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>domain:corner-writers.blog</t>
+          <t>domain:domraider.gb.net</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>corner-writers.blog</t>
+          <t>domraider.gb.net</t>
         </is>
       </c>
       <c r="C937" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>104.21.84.108</t>
+          <t>172.67.168.81</t>
         </is>
       </c>
       <c r="E937" t="inlineStr"/>
       <c r="F937" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (article/writer farm, .blog TLD)</t>
+          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (subdomain host zero authority)</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>domain:coruzants.com</t>
+          <t>domain:domraider.it.com</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>coruzants.com</t>
+          <t>domraider.it.com</t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>172.67.192.96</t>
+          <t>104.21.1.165</t>
         </is>
       </c>
       <c r="E938" t="inlineStr"/>
       <c r="F938" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS0)</t>
         </is>
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, nonsense name, single-day)</t>
+          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (Throwaway TLD)</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>domain:cvillico.com</t>
+          <t>domain:echoz.pages.dev</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>cvillico.com</t>
+          <t>echoz.pages.dev</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -32923,7 +32911,7 @@
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>104.21.14.64</t>
+          <t>172.66.47.143</t>
         </is>
       </c>
       <c r="E939" t="inlineStr"/>
@@ -32934,50 +32922,54 @@
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic name, no relevance)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev host)</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>domain:daily-hacks.pages.dev</t>
+          <t>domain:factmags.com</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>daily-hacks.pages.dev</t>
+          <t>factmags.com</t>
         </is>
       </c>
       <c r="C940" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>172.66.44.243</t>
-        </is>
-      </c>
-      <c r="E940" t="inlineStr"/>
+          <t>203.161.54.114</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, content-farm name)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Generic foreign article mill irrelevant)</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>domain:decoratingmom.com</t>
+          <t>domain:fashionclothingnews.com</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>decoratingmom.com</t>
+          <t>fashionclothingnews.com</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -32985,7 +32977,7 @@
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>172.67.201.81</t>
+          <t>172.67.156.33</t>
         </is>
       </c>
       <c r="E941" t="inlineStr"/>
@@ -32996,19 +32988,19 @@
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Interior-decor blog, off-topic, farm pattern)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic off-topic content)</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>domain:decoratingnerds.com</t>
+          <t>domain:fastlifesite.com</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>decoratingnerds.com</t>
+          <t>fastlifesite.com</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -33016,7 +33008,7 @@
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>172.67.144.130</t>
+          <t>172.67.176.248</t>
         </is>
       </c>
       <c r="E942" t="inlineStr"/>
@@ -33027,58 +33019,58 @@
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Interior-decor blog, off-topic, farm pattern)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic low authority)</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>domain:developmentmi.com</t>
+          <t>domain:findabusinessthat.com</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>developmentmi.com</t>
+          <t>findabusinessthat.com</t>
         </is>
       </c>
       <c r="C943" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>104.21.89.233</t>
+          <t>172.67.146.82</t>
         </is>
       </c>
       <c r="E943" t="inlineStr"/>
       <c r="F943" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS5)</t>
         </is>
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (generic name; no relevance AS6)</t>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (Directory-style spam name)</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>domain:divisionesmodularesjq.com</t>
+          <t>domain:findbiz.info</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>divisionesmodularesjq.com</t>
+          <t>findbiz.info</t>
         </is>
       </c>
       <c r="C944" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>162.215.210.151</t>
+          <t>185.139.128.92</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -33088,152 +33080,152 @@
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Spanish off-topic modular; irrelevant)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic directory name low authority)</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>domain:domraider.eu.com</t>
+          <t>domain:findtor.com</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>domraider.eu.com</t>
+          <t>findtor.com</t>
         </is>
       </c>
       <c r="C945" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>172.67.212.236</t>
-        </is>
-      </c>
-      <c r="E945" t="inlineStr"/>
+          <t>3.132.208.69</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (AS0, generic domain-hack TLD, no relevance)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic name)</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>domain:domraider.gb.net</t>
+          <t>domain:fixhubs.net</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>domraider.gb.net</t>
+          <t>fixhubs.net</t>
         </is>
       </c>
       <c r="C946" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>172.67.168.81</t>
+          <t>172.67.139.28</t>
         </is>
       </c>
       <c r="E946" t="inlineStr"/>
       <c r="F946" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (AS0, generic domain-hack TLD, no relevance)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic; very low authority)</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>domain:domraider.it.com</t>
+          <t>domain:flamingos.pages.dev</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>domraider.it.com</t>
+          <t>flamingos.pages.dev</t>
         </is>
       </c>
       <c r="C947" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>104.21.1.165</t>
+          <t>172.66.44.138</t>
         </is>
       </c>
       <c r="E947" t="inlineStr"/>
       <c r="F947" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS0)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>very-low-authority(AS0); weak signal — human QA; QA agent → TOXIC (AS0, generic domain-hack TLD, no relevance)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (throwaway pages.dev host)</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>domain:dowjones.io</t>
+          <t>domain:ggmap.co.com</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>dowjones.io</t>
+          <t>ggmap.co.com</t>
         </is>
       </c>
       <c r="C948" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>192.0.66.208</t>
-        </is>
-      </c>
-      <c r="E948" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.131.117</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr"/>
       <c r="F948" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Dow Jones brand impersonation typo)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Throwaway single-day generic .co.com domain)</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>domain:echoz.pages.dev</t>
+          <t>domain:ggmap.us.com</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>echoz.pages.dev</t>
+          <t>ggmap.us.com</t>
         </is>
       </c>
       <c r="C949" t="n">
@@ -33241,7 +33233,7 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>172.66.47.143</t>
+          <t>172.67.211.186</t>
         </is>
       </c>
       <c r="E949" t="inlineStr"/>
@@ -33252,85 +33244,81 @@
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic us.com subdomain; low authority)</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>domain:entrepreneurscruise.com</t>
+          <t>domain:global-rank.pages.dev</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>entrepreneurscruise.com</t>
+          <t>global-rank.pages.dev</t>
         </is>
       </c>
       <c r="C950" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>104.21.31.149</t>
+          <t>172.66.44.155</t>
         </is>
       </c>
       <c r="E950" t="inlineStr"/>
       <c r="F950" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (business content farm, off-topic)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev host shared cluster)</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>domain:eurekster.com</t>
+          <t>domain:global-ranks.pages.dev</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>eurekster.com</t>
+          <t>global-ranks.pages.dev</t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>170.9.240.198</t>
-        </is>
-      </c>
-      <c r="E951" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.66.44.110</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr"/>
       <c r="F951" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (defunct brand; 122 sitewide irrelevant links)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev; rank scheme)</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>domain:factmags.com</t>
+          <t>domain:global-websites.pages.dev</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>factmags.com</t>
+          <t>global-websites.pages.dev</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -33338,14 +33326,10 @@
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>203.161.54.114</t>
-        </is>
-      </c>
-      <c r="E952" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.66.47.78</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr"/>
       <c r="F952" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS4)</t>
@@ -33353,217 +33337,213 @@
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (article magazine farm; shared IP with goooogla)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev host)</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>domain:fashionclothingnews.com</t>
+          <t>domain:goooogla.com</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>fashionclothingnews.com</t>
+          <t>goooogla.com</t>
         </is>
       </c>
       <c r="C953" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>172.67.156.33</t>
-        </is>
-      </c>
-      <c r="E953" t="inlineStr"/>
+          <t>203.161.54.114</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (fashion news content farm, off-topic)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Nonsense Google-typo domain shared IP)</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>domain:fastlifesite.com</t>
+          <t>domain:greattraveladvisor.com</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>fastlifesite.com</t>
+          <t>greattraveladvisor.com</t>
         </is>
       </c>
       <c r="C954" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>172.67.176.248</t>
-        </is>
-      </c>
-      <c r="E954" t="inlineStr"/>
+          <t>107.180.2.227</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic content farm, single-day)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Generic travel content site no relevance)</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>domain:findabusinessthat.com</t>
+          <t>domain:harian24.com</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>findabusinessthat.com</t>
+          <t>harian24.com</t>
         </is>
       </c>
       <c r="C955" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>172.67.146.82</t>
+          <t>104.21.65.94</t>
         </is>
       </c>
       <c r="E955" t="inlineStr"/>
       <c r="F955" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS5)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (generic business directory farm)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Foreign site)</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>domain:findbiz.info</t>
+          <t>domain:hotonlinegaming.com</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>findbiz.info</t>
+          <t>hotonlinegaming.com</t>
         </is>
       </c>
       <c r="C956" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>185.139.128.92</t>
-        </is>
-      </c>
-      <c r="E956" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.129.112</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr"/>
       <c r="F956" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (business directory farm, .info)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Online gambling vertical)</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>domain:findingfarina.com</t>
+          <t>domain:huldra.pages.dev</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>findingfarina.com</t>
+          <t>huldra.pages.dev</t>
         </is>
       </c>
       <c r="C957" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>145.223.106.169</t>
-        </is>
-      </c>
-      <c r="E957" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.66.44.118</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr"/>
       <c r="F957" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS5)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (off-topic personal blog; AS5)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev host)</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>domain:findtor.com</t>
+          <t>domain:isardomains.com</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>findtor.com</t>
+          <t>isardomains.com</t>
         </is>
       </c>
       <c r="C958" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>3.132.208.69</t>
-        </is>
-      </c>
-      <c r="E958" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.48.247</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr"/>
       <c r="F958" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic name, no relevance)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Domain sales)</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>domain:fixhubs.net</t>
+          <t>domain:israelmilitaria.blogspot.com</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>fixhubs.net</t>
+          <t>israelmilitaria.blogspot.com</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -33571,10 +33551,14 @@
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>172.67.139.28</t>
-        </is>
-      </c>
-      <c r="E959" t="inlineStr"/>
+          <t>142.251.167.132</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F959" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -33582,19 +33566,19 @@
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic 'fix hub' template farm)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Irrelevant militaria blogspot spam links)</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>domain:flamingos.pages.dev</t>
+          <t>domain:ivcfddhbsa.blogspot.com</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>flamingos.pages.dev</t>
+          <t>ivcfddhbsa.blogspot.com</t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -33602,10 +33586,14 @@
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>172.66.44.138</t>
-        </is>
-      </c>
-      <c r="E960" t="inlineStr"/>
+          <t>192.178.218.132</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F960" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -33613,85 +33601,85 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Randomized nonsense hostname)</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>domain:gardenshaper.com</t>
+          <t>domain:jobsapp.info</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>gardenshaper.com</t>
+          <t>jobsapp.info</t>
         </is>
       </c>
       <c r="C961" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>198.20.115.3</t>
-        </is>
-      </c>
-      <c r="E961" t="inlineStr">
-        <is>
-          <t>nl</t>
-        </is>
-      </c>
+          <t>172.67.128.71</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr"/>
       <c r="F961" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS6)</t>
         </is>
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (garden-ish but foreign NL, generic)</t>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (generic jobs directory low authority)</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>domain:ggmap.co.com</t>
+          <t>domain:landscapeatlas.com</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>ggmap.co.com</t>
+          <t>landscapeatlas.com</t>
         </is>
       </c>
       <c r="C962" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>172.67.131.117</t>
-        </is>
-      </c>
-      <c r="E962" t="inlineStr"/>
+          <t>216.150.1.1</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS6)</t>
         </is>
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic domain-hack .co.com)</t>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Programmatic landscaping city-page directory; low authority)</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>domain:ggmap.us.com</t>
+          <t>domain:lawyerinjeddah.com</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>ggmap.us.com</t>
+          <t>lawyerinjeddah.com</t>
         </is>
       </c>
       <c r="C963" t="n">
@@ -33699,7 +33687,7 @@
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>172.67.211.186</t>
+          <t>104.21.36.238</t>
         </is>
       </c>
       <c r="E963" t="inlineStr"/>
@@ -33710,19 +33698,19 @@
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic domain-hack .us.com)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Foreign)</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>domain:gladeflowers.com</t>
+          <t>domain:libyanatravel.com</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>gladeflowers.com</t>
+          <t>libyanatravel.com</t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -33730,7 +33718,7 @@
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>104.21.74.93</t>
+          <t>104.21.70.241</t>
         </is>
       </c>
       <c r="E964" t="inlineStr"/>
@@ -33741,182 +33729,178 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (AS2, generic, single-day)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic foreign travel site shared cluster)</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>domain:global-rank.pages.dev</t>
+          <t>domain:localbizsphere.com</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>global-rank.pages.dev</t>
+          <t>localbizsphere.com</t>
         </is>
       </c>
       <c r="C965" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>172.66.44.155</t>
-        </is>
-      </c>
-      <c r="E965" t="inlineStr"/>
+          <t>51.81.59.247</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (SEO rank name; pages.dev throwaway host)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic directory name)</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>domain:global-ranks.pages.dev</t>
+          <t>domain:localbizzz.com</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>global-ranks.pages.dev</t>
+          <t>localbizzz.com</t>
         </is>
       </c>
       <c r="C966" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>172.66.44.110</t>
+          <t>104.21.33.48</t>
         </is>
       </c>
       <c r="E966" t="inlineStr"/>
       <c r="F966" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (SEO rank name; pages.dev throwaway host)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic directory low authority)</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>domain:global-websites.pages.dev</t>
+          <t>domain:marketingupdatee.com</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>global-websites.pages.dev</t>
+          <t>marketingupdatee.com</t>
         </is>
       </c>
       <c r="C967" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>172.66.47.78</t>
+          <t>172.67.166.117</t>
         </is>
       </c>
       <c r="E967" t="inlineStr"/>
       <c r="F967" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (SEO/directory name; pages.dev throwaway host)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Marketing/SEO spam name)</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>domain:goooogla.com</t>
+          <t>domain:masihnyata.com</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>goooogla.com</t>
+          <t>masihnyata.com</t>
         </is>
       </c>
       <c r="C968" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>203.161.54.114</t>
-        </is>
-      </c>
-      <c r="E968" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.149.19</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr"/>
       <c r="F968" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Google typosquat; shared IP farm)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Foreign generic content)</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>domain:greattraveladvisor.com</t>
+          <t>domain:mediaboooster.com</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>greattraveladvisor.com</t>
+          <t>mediaboooster.com</t>
         </is>
       </c>
       <c r="C969" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>107.180.2.227</t>
-        </is>
-      </c>
-      <c r="E969" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.14.45</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr"/>
       <c r="F969" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS5)</t>
         </is>
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (travel off-topic generic commercial name)</t>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (Misspelled media/SEO spam name)</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>domain:harian24.com</t>
+          <t>domain:mymarketpost.com</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>harian24.com</t>
+          <t>mymarketpost.com</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -33924,7 +33908,7 @@
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>104.21.65.94</t>
+          <t>172.67.159.15</t>
         </is>
       </c>
       <c r="E970" t="inlineStr"/>
@@ -33935,50 +33919,50 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Indonesian news, off-topic foreign)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic content-spam name)</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>domain:hotonlinegaming.com</t>
+          <t>domain:newsblogsports.site</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>hotonlinegaming.com</t>
+          <t>newsblogsports.site</t>
         </is>
       </c>
       <c r="C971" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>172.67.129.112</t>
+          <t>172.67.220.122</t>
         </is>
       </c>
       <c r="E971" t="inlineStr"/>
       <c r="F971" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (gambling/gaming off-topic high-risk vertical)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic content)</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>domain:huldra.pages.dev</t>
+          <t>domain:obake.pages.dev</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>huldra.pages.dev</t>
+          <t>obake.pages.dev</t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -33986,7 +33970,7 @@
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>172.66.44.118</t>
+          <t>172.66.44.72</t>
         </is>
       </c>
       <c r="E972" t="inlineStr"/>
@@ -33997,50 +33981,54 @@
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev host)</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>domain:isardomains.com</t>
+          <t>domain:onlinelocalbrand.com</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>isardomains.com</t>
+          <t>onlinelocalbrand.com</t>
         </is>
       </c>
       <c r="C973" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>104.21.48.247</t>
-        </is>
-      </c>
-      <c r="E973" t="inlineStr"/>
+          <t>185.163.16.3</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (domain-reseller/directory name; link scheme signal)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic name)</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>domain:israelmilitaria.blogspot.com</t>
+          <t>domain:onlineshoppingidea.com</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>israelmilitaria.blogspot.com</t>
+          <t>onlineshoppingidea.com</t>
         </is>
       </c>
       <c r="C974" t="n">
@@ -34048,14 +34036,10 @@
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>142.251.167.132</t>
-        </is>
-      </c>
-      <c r="E974" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.20.72</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr"/>
       <c r="F974" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -34063,19 +34047,19 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (blogspot militaria, off-topic, 60 sitewide links)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Generic shopping content; low authority)</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>domain:ivcfddhbsa.blogspot.com</t>
+          <t>domain:pingeras.blogspot.com</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>ivcfddhbsa.blogspot.com</t>
+          <t>pingeras.blogspot.com</t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -34083,7 +34067,7 @@
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>192.178.218.132</t>
+          <t>142.251.163.132</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
@@ -34098,58 +34082,58 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (gibberish blogspot subdomain)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Spam Blogspot blog)</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>domain:jobsapp.info</t>
+          <t>domain:plrdownloadshub.com</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>jobsapp.info</t>
+          <t>plrdownloadshub.com</t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>172.67.128.71</t>
+          <t>172.67.166.90</t>
         </is>
       </c>
       <c r="E976" t="inlineStr"/>
       <c r="F976" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (jobs off-topic; .info low authority)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (PLR downloads spam)</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>domain:keirseybooks.com</t>
+          <t>domain:poshcoloringstudiostorer.blogspot.com</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>keirseybooks.com</t>
+          <t>poshcoloringstudiostorer.blogspot.com</t>
         </is>
       </c>
       <c r="C977" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>107.180.3.106</t>
+          <t>142.251.167.132</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
@@ -34159,24 +34143,24 @@
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (books off-topic; AS6)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Spam blogspot nonsense name)</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>domain:lawyerinjeddah.com</t>
+          <t>domain:quotesblom.com</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>lawyerinjeddah.com</t>
+          <t>quotesblom.com</t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -34184,7 +34168,7 @@
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>104.21.36.238</t>
+          <t>104.21.14.53</t>
         </is>
       </c>
       <c r="E978" t="inlineStr"/>
@@ -34195,19 +34179,19 @@
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Jeddah lawyer, off-topic foreign)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Random brand; single-day; low authority)</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>domain:libyanatravel.com</t>
+          <t>domain:realtalkaj.me</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>libyanatravel.com</t>
+          <t>realtalkaj.me</t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -34215,10 +34199,14 @@
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>104.21.70.241</t>
-        </is>
-      </c>
-      <c r="E979" t="inlineStr"/>
+          <t>192.0.78.25</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F979" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -34226,27 +34214,27 @@
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Libya travel, off-topic foreign)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Personal blog)</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>domain:localbizsphere.com</t>
+          <t>domain:revan-me.com</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>localbizsphere.com</t>
+          <t>revan-me.com</t>
         </is>
       </c>
       <c r="C980" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>51.81.59.247</t>
+          <t>160.153.129.19</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
@@ -34256,24 +34244,24 @@
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (local business directory farm)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Generic name)</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>domain:localbizzz.com</t>
+          <t>domain:reviewmx.com</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>localbizzz.com</t>
+          <t>reviewmx.com</t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -34281,7 +34269,7 @@
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>104.21.33.48</t>
+          <t>172.67.164.204</t>
         </is>
       </c>
       <c r="E981" t="inlineStr"/>
@@ -34292,54 +34280,50 @@
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (local business directory farm)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Review-spam name)</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>domain:lovetravellife.com</t>
+          <t>domain:royaldb.us.com</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>lovetravellife.com</t>
+          <t>royaldb.us.com</t>
         </is>
       </c>
       <c r="C982" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>108.181.247.75</t>
-        </is>
-      </c>
-      <c r="E982" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.87.48</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr"/>
       <c r="F982" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G982" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (travel off-topic; AS4)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Throwaway us.com host brand-new single-day)</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>domain:marketingupdatee.com</t>
+          <t>domain:shoplogist.com</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>marketingupdatee.com</t>
+          <t>shoplogist.com</t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -34347,7 +34331,7 @@
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>172.67.166.117</t>
+          <t>172.67.180.152</t>
         </is>
       </c>
       <c r="E983" t="inlineStr"/>
@@ -34358,182 +34342,182 @@
       </c>
       <c r="G983" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (marketing content farm)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic low authority)</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>domain:masihnyata.com</t>
+          <t>domain:slapshady.com</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>masihnyata.com</t>
+          <t>slapshady.com</t>
         </is>
       </c>
       <c r="C984" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>172.67.149.19</t>
-        </is>
-      </c>
-      <c r="E984" t="inlineStr"/>
+          <t>208.109.22.214</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Indonesian site, off-topic foreign)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (generic unknown no relevance)</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>domain:mediaboooster.com</t>
+          <t>domain:snowlawn.net</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>mediaboooster.com</t>
+          <t>snowlawn.net</t>
         </is>
       </c>
       <c r="C985" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>104.21.14.45</t>
-        </is>
-      </c>
-      <c r="E985" t="inlineStr"/>
+          <t>216.239.34.21</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS5)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (link/media-boost SEO service name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Programmatic snow/lawn lead-gen directory; thin auto-pages)</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>domain:medidocs.com</t>
+          <t>domain:sportsbikeparts.pk</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>medidocs.com</t>
+          <t>sportsbikeparts.pk</t>
         </is>
       </c>
       <c r="C986" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>72.167.102.111</t>
-        </is>
-      </c>
-      <c r="E986" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.167.23</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr"/>
       <c r="F986" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:very-low-authority(AS2)</t>
         </is>
       </c>
       <c r="G986" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (medical off-topic; AS4)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Pakistan site; no relevance)</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>domain:mygirlyspace.com</t>
+          <t>domain:starcourts.com</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>mygirlyspace.com</t>
+          <t>starcourts.com</t>
         </is>
       </c>
       <c r="C987" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>31.170.166.36</t>
-        </is>
-      </c>
-      <c r="E987" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.68.102</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr"/>
       <c r="F987" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:very-low-authority(AS6)</t>
         </is>
       </c>
       <c r="G987" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (off-topic lifestyle; AS3 low authority)</t>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (threat-intel flagged no real site)</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>domain:mymarketpost.com</t>
+          <t>domain:startupwebsolutions.com.au</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>mymarketpost.com</t>
+          <t>startupwebsolutions.com.au</t>
         </is>
       </c>
       <c r="C988" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>172.67.159.15</t>
+          <t>172.67.138.213</t>
         </is>
       </c>
       <c r="E988" t="inlineStr"/>
       <c r="F988" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G988" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (PR/market post content farm)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Generic SEO/web agency)</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>domain:naturalegno.net</t>
+          <t>domain:studartcorrea.com.br</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>naturalegno.net</t>
+          <t>studartcorrea.com.br</t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -34541,7 +34525,7 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>104.21.93.87</t>
+          <t>172.67.196.110</t>
         </is>
       </c>
       <c r="E989" t="inlineStr"/>
@@ -34552,50 +34536,54 @@
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Italian wood site, off-topic foreign)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (real firm but spam-injected pages)</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>domain:newsblogsports.site</t>
+          <t>domain:theambiencenews.com</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>newsblogsports.site</t>
+          <t>theambiencenews.com</t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>172.67.220.122</t>
-        </is>
-      </c>
-      <c r="E990" t="inlineStr"/>
+          <t>198.12.232.179</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS6)</t>
         </is>
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (spam TLD .site, news/sports farm)</t>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Single-day throwaway news post on cheap host)</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>domain:obake.pages.dev</t>
+          <t>domain:themicrodigits.com</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>obake.pages.dev</t>
+          <t>themicrodigits.com</t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -34603,7 +34591,7 @@
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>172.66.44.72</t>
+          <t>104.21.71.254</t>
         </is>
       </c>
       <c r="E991" t="inlineStr"/>
@@ -34614,19 +34602,19 @@
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (free pages.dev host, nonsense name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic brand-new low authority)</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>domain:onlinelocalbrand.com</t>
+          <t>domain:thetarotalk.com</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>onlinelocalbrand.com</t>
+          <t>thetarotalk.com</t>
         </is>
       </c>
       <c r="C992" t="n">
@@ -34634,14 +34622,10 @@
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>185.163.16.3</t>
-        </is>
-      </c>
-      <c r="E992" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.166.149</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr"/>
       <c r="F992" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -34649,50 +34633,50 @@
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (marketing/branding farm name)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Tarot blog)</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>domain:onlineshoppingidea.com</t>
+          <t>domain:turfinstallpros.com</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>onlineshoppingidea.com</t>
+          <t>turfinstallpros.com</t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>104.21.20.72</t>
+          <t>104.21.20.231</t>
         </is>
       </c>
       <c r="E993" t="inlineStr"/>
       <c r="F993" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (shopping content farm, off-topic)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Thin programmatic turf-installer advertising directory)</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>domain:phanerosart.com</t>
+          <t>domain:ultimatelistzone.com</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>phanerosart.com</t>
+          <t>ultimatelistzone.com</t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -34700,10 +34684,14 @@
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>104.21.56.40</t>
-        </is>
-      </c>
-      <c r="E994" t="inlineStr"/>
+          <t>167.114.32.229</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F994" t="inlineStr">
         <is>
           <t>qa-override:very-low-authority(AS2)</t>
@@ -34711,221 +34699,213 @@
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (art site, off-topic, single-day)</t>
+          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Listing spam name)</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>domain:pingeras.blogspot.com</t>
+          <t>domain:usapridenetwork.us</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>pingeras.blogspot.com</t>
+          <t>usapridenetwork.us</t>
         </is>
       </c>
       <c r="C995" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>142.251.163.132</t>
-        </is>
-      </c>
-      <c r="E995" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>172.67.179.136</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr"/>
       <c r="F995" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS6)</t>
         </is>
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (blogspot, generic, 14 links)</t>
+          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Automotive content farm; name/content mismatch)</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>domain:plrdownloadshub.com</t>
+          <t>domain:webbys.pages.dev</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>plrdownloadshub.com</t>
+          <t>webbys.pages.dev</t>
         </is>
       </c>
       <c r="C996" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>172.67.166.90</t>
+          <t>172.66.47.196</t>
         </is>
       </c>
       <c r="E996" t="inlineStr"/>
       <c r="F996" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS4)</t>
         </is>
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (PLR downloads, spam vertical)</t>
+          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (Throwaway pages.dev host)</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>domain:plumeriamarketing.com</t>
+          <t>domain:webhubsites.com</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>plumeriamarketing.com</t>
+          <t>webhubsites.com</t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>104.21.15.10</t>
+          <t>172.67.192.40</t>
         </is>
       </c>
       <c r="E997" t="inlineStr"/>
       <c r="F997" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS5)</t>
         </is>
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (marketing agency, off-topic)</t>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (Generic sites-name)</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>domain:popularask.net</t>
+          <t>domain:wecelebrities.com</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>popularask.net</t>
+          <t>wecelebrities.com</t>
         </is>
       </c>
       <c r="C998" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>104.21.23.20</t>
+          <t>172.67.199.73</t>
         </is>
       </c>
       <c r="E998" t="inlineStr"/>
       <c r="F998" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS6)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (Q&amp;A article farm; off-topic)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (Generic celebrity content)</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>domain:poshcoloringstudiostorer.blogspot.com</t>
+          <t>domain:worldlinksites.com</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>poshcoloringstudiostorer.blogspot.com</t>
+          <t>worldlinksites.com</t>
         </is>
       </c>
       <c r="C999" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>142.251.167.132</t>
-        </is>
-      </c>
-      <c r="E999" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>104.21.11.111</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr"/>
       <c r="F999" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS5)</t>
         </is>
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (blogspot, off-topic coloring, odd name)</t>
+          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (Generic link-scheme name)</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>domain:quotesblom.com</t>
+          <t>domain:writfy.com</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>quotesblom.com</t>
+          <t>writfy.com</t>
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>104.21.14.53</t>
+          <t>104.21.57.78</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr"/>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:very-low-authority(AS3)</t>
         </is>
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (quotes content farm, single-day)</t>
+          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (crypto/SEO article content farm)</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>domain:realtalkaj.me</t>
+          <t>domain:reputablebusinesses.com</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>realtalkaj.me</t>
+          <t>reputablebusinesses.com</t>
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>192.0.78.25</t>
+          <t>145.223.126.72</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -34935,32 +34915,32 @@
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic personal .me blog)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (Directory-style)</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>domain:revan-me.com</t>
+          <t>domain:resonancelabjo.com</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>revan-me.com</t>
+          <t>resonancelabjo.com</t>
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>160.153.129.19</t>
+          <t>160.153.133.225</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -34970,129 +34950,133 @@
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS3)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1002" t="inlineStr">
         <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (AS3 randomized nonsense name; irrelevant)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (Random nonsense brand name; no presence)</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>domain:reviewmx.com</t>
+          <t>domain:semalt.ai</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>reviewmx.com</t>
+          <t>semalt.ai</t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>172.67.164.204</t>
-        </is>
-      </c>
-      <c r="E1003" t="inlineStr"/>
+          <t>185.100.234.251</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>nl</t>
+        </is>
+      </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (review farm name)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (known SEO/referral spam operation)</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>domain:robuta.com</t>
+          <t>domain:southernlanka.lk</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>robuta.com</t>
+          <t>southernlanka.lk</t>
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>162.159.140.164</t>
+          <t>135.181.210.47</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS5)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (brandable nonsense; no relevance)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (Foreign Sri Lanka site irrelevant to client)</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>domain:royaldb.us.com</t>
+          <t>domain:sportmediaset.co</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>royaldb.us.com</t>
+          <t>sportmediaset.co</t>
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>104.21.87.48</t>
+          <t>172.67.192.199</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr"/>
       <c r="F1005" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1005" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic .us.com, single-day)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (Knockoff of real sportmediaset.it shared cluster)</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>domain:rumoursnews.com</t>
+          <t>domain:thenllc.ca</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>rumoursnews.com</t>
+          <t>thenllc.ca</t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>217.196.54.177</t>
+          <t>156.67.77.68</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -35102,98 +35086,94 @@
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1006" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (gossip news content farm)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (Generic Canadian shell; no relevance)</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>domain:shoplogist.com</t>
+          <t>domain:viral-status.com</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>shoplogist.com</t>
+          <t>viral-status.com</t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>172.67.180.152</t>
+          <t>104.21.72.65</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr"/>
       <c r="F1007" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS2)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic shop/logistics name)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (Generic viral content)</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>domain:sisgroup.lk</t>
+          <t>domain:wealthyoverview.com</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>sisgroup.lk</t>
+          <t>wealthyoverview.com</t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>194.233.75.17</t>
-        </is>
-      </c>
-      <c r="E1008" t="inlineStr">
-        <is>
-          <t>sg</t>
-        </is>
-      </c>
+          <t>172.67.130.236</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr"/>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>qa-override:foreign-geo-cluster(sg)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1008" t="inlineStr">
         <is>
-          <t>foreign-geo-cluster(sg); weak signal — human QA; QA agent → TOXIC (Sri Lanka foreign cluster; off-topic)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (Generic finance content on Cloudflare)</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>domain:slapshady.com</t>
+          <t>domain:websitescrawl.com</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>slapshady.com</t>
+          <t>websitescrawl.com</t>
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>208.109.22.214</t>
+          <t>68.178.235.175</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -35203,1791 +35183,17 @@
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t>qa-override:very-low-authority(AS4)</t>
+          <t>qa-override:unclassified</t>
         </is>
       </c>
       <c r="G1009" t="inlineStr">
         <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (AS4 nonsense name; irrelevant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1010">
-      <c r="A1010" t="inlineStr">
-        <is>
-          <t>domain:sportsbikeparts.pk</t>
-        </is>
-      </c>
-      <c r="B1010" t="inlineStr">
-        <is>
-          <t>sportsbikeparts.pk</t>
-        </is>
-      </c>
-      <c r="C1010" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1010" t="inlineStr">
-        <is>
-          <t>172.67.167.23</t>
-        </is>
-      </c>
-      <c r="E1010" t="inlineStr"/>
-      <c r="F1010" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1010" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Pakistan bike parts, off-topic foreign)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1011">
-      <c r="A1011" t="inlineStr">
-        <is>
-          <t>domain:starcourts.com</t>
-        </is>
-      </c>
-      <c r="B1011" t="inlineStr">
-        <is>
-          <t>starcourts.com</t>
-        </is>
-      </c>
-      <c r="C1011" t="n">
-        <v>6</v>
-      </c>
-      <c r="D1011" t="inlineStr">
-        <is>
-          <t>104.21.68.102</t>
-        </is>
-      </c>
-      <c r="E1011" t="inlineStr"/>
-      <c r="F1011" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS6)</t>
-        </is>
-      </c>
-      <c r="G1011" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (generic nonsense name; no relevance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1012">
-      <c r="A1012" t="inlineStr">
-        <is>
-          <t>domain:startupwebsolutions.com.au</t>
-        </is>
-      </c>
-      <c r="B1012" t="inlineStr">
-        <is>
-          <t>startupwebsolutions.com.au</t>
-        </is>
-      </c>
-      <c r="C1012" t="n">
-        <v>4</v>
-      </c>
-      <c r="D1012" t="inlineStr">
-        <is>
-          <t>172.67.138.213</t>
-        </is>
-      </c>
-      <c r="E1012" t="inlineStr"/>
-      <c r="F1012" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS4)</t>
-        </is>
-      </c>
-      <c r="G1012" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (generic SEO/web-agency name; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1013">
-      <c r="A1013" t="inlineStr">
-        <is>
-          <t>domain:studartcorrea.com.br</t>
-        </is>
-      </c>
-      <c r="B1013" t="inlineStr">
-        <is>
-          <t>studartcorrea.com.br</t>
-        </is>
-      </c>
-      <c r="C1013" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1013" t="inlineStr">
-        <is>
-          <t>172.67.196.110</t>
-        </is>
-      </c>
-      <c r="E1013" t="inlineStr"/>
-      <c r="F1013" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1013" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Brazil art studio, off-topic foreign)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1014">
-      <c r="A1014" t="inlineStr">
-        <is>
-          <t>domain:tapalmbeaches.com</t>
-        </is>
-      </c>
-      <c r="B1014" t="inlineStr">
-        <is>
-          <t>tapalmbeaches.com</t>
-        </is>
-      </c>
-      <c r="C1014" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1014" t="inlineStr">
-        <is>
-          <t>104.18.20.240</t>
-        </is>
-      </c>
-      <c r="E1014" t="inlineStr"/>
-      <c r="F1014" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1014" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (off-topic location site, generic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1015">
-      <c r="A1015" t="inlineStr">
-        <is>
-          <t>domain:techsb.ca</t>
-        </is>
-      </c>
-      <c r="B1015" t="inlineStr">
-        <is>
-          <t>techsb.ca</t>
-        </is>
-      </c>
-      <c r="C1015" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1015" t="inlineStr">
-        <is>
-          <t>35.212.103.243</t>
-        </is>
-      </c>
-      <c r="E1015" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1015" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1015" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic tech name, off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1016">
-      <c r="A1016" t="inlineStr">
-        <is>
-          <t>domain:theambiencenews.com</t>
-        </is>
-      </c>
-      <c r="B1016" t="inlineStr">
-        <is>
-          <t>theambiencenews.com</t>
-        </is>
-      </c>
-      <c r="C1016" t="n">
-        <v>6</v>
-      </c>
-      <c r="D1016" t="inlineStr">
-        <is>
-          <t>198.12.232.179</t>
-        </is>
-      </c>
-      <c r="E1016" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1016" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS6)</t>
-        </is>
-      </c>
-      <c r="G1016" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (news article farm; one-day link)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1017">
-      <c r="A1017" t="inlineStr">
-        <is>
-          <t>domain:thecloudherald.com</t>
-        </is>
-      </c>
-      <c r="B1017" t="inlineStr">
-        <is>
-          <t>thecloudherald.com</t>
-        </is>
-      </c>
-      <c r="C1017" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1017" t="inlineStr">
-        <is>
-          <t>172.66.47.22</t>
-        </is>
-      </c>
-      <c r="E1017" t="inlineStr"/>
-      <c r="F1017" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1017" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic news content farm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1018">
-      <c r="A1018" t="inlineStr">
-        <is>
-          <t>domain:thehomefixhub.com</t>
-        </is>
-      </c>
-      <c r="B1018" t="inlineStr">
-        <is>
-          <t>thehomefixhub.com</t>
-        </is>
-      </c>
-      <c r="C1018" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1018" t="inlineStr">
-        <is>
-          <t>172.67.142.210</t>
-        </is>
-      </c>
-      <c r="E1018" t="inlineStr"/>
-      <c r="F1018" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1018" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC ('home fix hub' template farm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1019">
-      <c r="A1019" t="inlineStr">
-        <is>
-          <t>domain:themicrodigits.com</t>
-        </is>
-      </c>
-      <c r="B1019" t="inlineStr">
-        <is>
-          <t>themicrodigits.com</t>
-        </is>
-      </c>
-      <c r="C1019" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1019" t="inlineStr">
-        <is>
-          <t>104.21.71.254</t>
-        </is>
-      </c>
-      <c r="E1019" t="inlineStr"/>
-      <c r="F1019" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1019" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic tech, single-day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1020">
-      <c r="A1020" t="inlineStr">
-        <is>
-          <t>domain:thetarotalk.com</t>
-        </is>
-      </c>
-      <c r="B1020" t="inlineStr">
-        <is>
-          <t>thetarotalk.com</t>
-        </is>
-      </c>
-      <c r="C1020" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1020" t="inlineStr">
-        <is>
-          <t>172.67.166.149</t>
-        </is>
-      </c>
-      <c r="E1020" t="inlineStr"/>
-      <c r="F1020" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1020" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (tarot site, off-topic vertical)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1021">
-      <c r="A1021" t="inlineStr">
-        <is>
-          <t>domain:turkiyelinux.com</t>
-        </is>
-      </c>
-      <c r="B1021" t="inlineStr">
-        <is>
-          <t>turkiyelinux.com</t>
-        </is>
-      </c>
-      <c r="C1021" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1021" t="inlineStr">
-        <is>
-          <t>46.20.34.203</t>
-        </is>
-      </c>
-      <c r="E1021" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F1021" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1021" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Turkey linux site, off-topic foreign)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1022">
-      <c r="A1022" t="inlineStr">
-        <is>
-          <t>domain:ultimatelistzone.com</t>
-        </is>
-      </c>
-      <c r="B1022" t="inlineStr">
-        <is>
-          <t>ultimatelistzone.com</t>
-        </is>
-      </c>
-      <c r="C1022" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1022" t="inlineStr">
-        <is>
-          <t>167.114.32.229</t>
-        </is>
-      </c>
-      <c r="E1022" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1022" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1022" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (listing/list-zone farm name)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" t="inlineStr">
-        <is>
-          <t>domain:unanswered.io</t>
-        </is>
-      </c>
-      <c r="B1023" t="inlineStr">
-        <is>
-          <t>unanswered.io</t>
-        </is>
-      </c>
-      <c r="C1023" t="n">
-        <v>5</v>
-      </c>
-      <c r="D1023" t="inlineStr">
-        <is>
-          <t>104.21.73.181</t>
-        </is>
-      </c>
-      <c r="E1023" t="inlineStr"/>
-      <c r="F1023" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS5)</t>
-        </is>
-      </c>
-      <c r="G1023" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (generic Q&amp;A; off-topic low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" t="inlineStr">
-        <is>
-          <t>domain:updatejakarta.com</t>
-        </is>
-      </c>
-      <c r="B1024" t="inlineStr">
-        <is>
-          <t>updatejakarta.com</t>
-        </is>
-      </c>
-      <c r="C1024" t="n">
-        <v>4</v>
-      </c>
-      <c r="D1024" t="inlineStr">
-        <is>
-          <t>104.21.34.221</t>
-        </is>
-      </c>
-      <c r="E1024" t="inlineStr"/>
-      <c r="F1024" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS4)</t>
-        </is>
-      </c>
-      <c r="G1024" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (foreign Jakarta news; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" t="inlineStr">
-        <is>
-          <t>domain:usapridenetwork.us</t>
-        </is>
-      </c>
-      <c r="B1025" t="inlineStr">
-        <is>
-          <t>usapridenetwork.us</t>
-        </is>
-      </c>
-      <c r="C1025" t="n">
-        <v>6</v>
-      </c>
-      <c r="D1025" t="inlineStr">
-        <is>
-          <t>172.67.179.136</t>
-        </is>
-      </c>
-      <c r="E1025" t="inlineStr"/>
-      <c r="F1025" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS6)</t>
-        </is>
-      </c>
-      <c r="G1025" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS6); weak signal — human QA; QA agent → TOXIC (generic network name; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" t="inlineStr">
-        <is>
-          <t>domain:webbys.pages.dev</t>
-        </is>
-      </c>
-      <c r="B1026" t="inlineStr">
-        <is>
-          <t>webbys.pages.dev</t>
-        </is>
-      </c>
-      <c r="C1026" t="n">
-        <v>4</v>
-      </c>
-      <c r="D1026" t="inlineStr">
-        <is>
-          <t>172.66.47.196</t>
-        </is>
-      </c>
-      <c r="E1026" t="inlineStr"/>
-      <c r="F1026" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS4)</t>
-        </is>
-      </c>
-      <c r="G1026" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (pages.dev throwaway; generic name)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" t="inlineStr">
-        <is>
-          <t>domain:webhubsites.com</t>
-        </is>
-      </c>
-      <c r="B1027" t="inlineStr">
-        <is>
-          <t>webhubsites.com</t>
-        </is>
-      </c>
-      <c r="C1027" t="n">
-        <v>5</v>
-      </c>
-      <c r="D1027" t="inlineStr">
-        <is>
-          <t>172.67.192.40</t>
-        </is>
-      </c>
-      <c r="E1027" t="inlineStr"/>
-      <c r="F1027" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS5)</t>
-        </is>
-      </c>
-      <c r="G1027" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (web-hub/directory name; link-scheme signal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" t="inlineStr">
-        <is>
-          <t>domain:wecelebrities.com</t>
-        </is>
-      </c>
-      <c r="B1028" t="inlineStr">
-        <is>
-          <t>wecelebrities.com</t>
-        </is>
-      </c>
-      <c r="C1028" t="n">
-        <v>3</v>
-      </c>
-      <c r="D1028" t="inlineStr">
-        <is>
-          <t>172.67.199.73</t>
-        </is>
-      </c>
-      <c r="E1028" t="inlineStr"/>
-      <c r="F1028" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS3)</t>
-        </is>
-      </c>
-      <c r="G1028" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (celebrity gossip off-topic; AS3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" t="inlineStr">
-        <is>
-          <t>domain:weedspots.net</t>
-        </is>
-      </c>
-      <c r="B1029" t="inlineStr">
-        <is>
-          <t>weedspots.net</t>
-        </is>
-      </c>
-      <c r="C1029" t="n">
-        <v>4</v>
-      </c>
-      <c r="D1029" t="inlineStr">
-        <is>
-          <t>165.227.88.129</t>
-        </is>
-      </c>
-      <c r="E1029" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1029" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS4)</t>
-        </is>
-      </c>
-      <c r="G1029" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS4); weak signal — human QA; QA agent → TOXIC (likely cannabis directory; off-topic risk)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" t="inlineStr">
-        <is>
-          <t>domain:willettonuniforms.com.au</t>
-        </is>
-      </c>
-      <c r="B1030" t="inlineStr">
-        <is>
-          <t>willettonuniforms.com.au</t>
-        </is>
-      </c>
-      <c r="C1030" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1030" t="inlineStr">
-        <is>
-          <t>104.21.48.84</t>
-        </is>
-      </c>
-      <c r="E1030" t="inlineStr"/>
-      <c r="F1030" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1030" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (Australia uniforms shop, off-topic foreign)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" t="inlineStr">
-        <is>
-          <t>domain:worldlinksites.com</t>
-        </is>
-      </c>
-      <c r="B1031" t="inlineStr">
-        <is>
-          <t>worldlinksites.com</t>
-        </is>
-      </c>
-      <c r="C1031" t="n">
-        <v>5</v>
-      </c>
-      <c r="D1031" t="inlineStr">
-        <is>
-          <t>104.21.11.111</t>
-        </is>
-      </c>
-      <c r="E1031" t="inlineStr"/>
-      <c r="F1031" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS5)</t>
-        </is>
-      </c>
-      <c r="G1031" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS5); weak signal — human QA; QA agent → TOXIC (link-farm/directory name; link scheme)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" t="inlineStr">
-        <is>
-          <t>domain:writfy.com</t>
-        </is>
-      </c>
-      <c r="B1032" t="inlineStr">
-        <is>
-          <t>writfy.com</t>
-        </is>
-      </c>
-      <c r="C1032" t="n">
-        <v>3</v>
-      </c>
-      <c r="D1032" t="inlineStr">
-        <is>
-          <t>104.21.57.78</t>
-        </is>
-      </c>
-      <c r="E1032" t="inlineStr"/>
-      <c r="F1032" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS3)</t>
-        </is>
-      </c>
-      <c r="G1032" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS3); weak signal — human QA; QA agent → TOXIC (AS3 nonsense/writing-mill name; irrelevant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" t="inlineStr">
-        <is>
-          <t>domain:yeow.ai</t>
-        </is>
-      </c>
-      <c r="B1033" t="inlineStr">
-        <is>
-          <t>yeow.ai</t>
-        </is>
-      </c>
-      <c r="C1033" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1033" t="inlineStr">
-        <is>
-          <t>157.230.165.86</t>
-        </is>
-      </c>
-      <c r="E1033" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1033" t="inlineStr">
-        <is>
-          <t>qa-override:very-low-authority(AS2)</t>
-        </is>
-      </c>
-      <c r="G1033" t="inlineStr">
-        <is>
-          <t>very-low-authority(AS2); weak signal — human QA; QA agent → TOXIC (generic .ai site, off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" t="inlineStr">
-        <is>
-          <t>domain:addresspage.com</t>
-        </is>
-      </c>
-      <c r="B1034" t="inlineStr">
-        <is>
-          <t>addresspage.com</t>
-        </is>
-      </c>
-      <c r="C1034" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1034" t="inlineStr">
-        <is>
-          <t>172.67.151.92</t>
-        </is>
-      </c>
-      <c r="E1034" t="inlineStr"/>
-      <c r="F1034" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1034" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (address listing directory; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" t="inlineStr">
-        <is>
-          <t>domain:buyatreechangealife.com</t>
-        </is>
-      </c>
-      <c r="B1035" t="inlineStr">
-        <is>
-          <t>buyatreechangealife.com</t>
-        </is>
-      </c>
-      <c r="C1035" t="n">
-        <v>18</v>
-      </c>
-      <c r="D1035" t="inlineStr">
-        <is>
-          <t>198.185.159.144</t>
-        </is>
-      </c>
-      <c r="E1035" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1035" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1035" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Aus lifestyle off-topic; irrelevant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" t="inlineStr">
-        <is>
-          <t>domain:designedbyai.io</t>
-        </is>
-      </c>
-      <c r="B1036" t="inlineStr">
-        <is>
-          <t>designedbyai.io</t>
-        </is>
-      </c>
-      <c r="C1036" t="n">
-        <v>18</v>
-      </c>
-      <c r="D1036" t="inlineStr">
-        <is>
-          <t>104.21.34.193</t>
-        </is>
-      </c>
-      <c r="E1036" t="inlineStr"/>
-      <c r="F1036" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1036" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (AI design tool off-topic; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" t="inlineStr">
-        <is>
-          <t>domain:dreamchaserhub.com</t>
-        </is>
-      </c>
-      <c r="B1037" t="inlineStr">
-        <is>
-          <t>dreamchaserhub.com</t>
-        </is>
-      </c>
-      <c r="C1037" t="n">
-        <v>13</v>
-      </c>
-      <c r="D1037" t="inlineStr">
-        <is>
-          <t>205.196.220.15</t>
-        </is>
-      </c>
-      <c r="E1037" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1037" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1037" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (generic hub off-topic; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="inlineStr">
-        <is>
-          <t>domain:ejobscircular.com</t>
-        </is>
-      </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>ejobscircular.com</t>
-        </is>
-      </c>
-      <c r="C1038" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1038" t="inlineStr">
-        <is>
-          <t>104.21.68.155</t>
-        </is>
-      </c>
-      <c r="E1038" t="inlineStr"/>
-      <c r="F1038" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1038" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Bangladesh jobs off-topic; foreign)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="inlineStr">
-        <is>
-          <t>domain:escuela-indecopi.edu.pe</t>
-        </is>
-      </c>
-      <c r="B1039" t="inlineStr">
-        <is>
-          <t>escuela-indecopi.edu.pe</t>
-        </is>
-      </c>
-      <c r="C1039" t="n">
-        <v>13</v>
-      </c>
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>173.212.231.25</t>
-        </is>
-      </c>
-      <c r="E1039" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F1039" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1039" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Peru edu hosted France; suspicious irrelevant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="inlineStr">
-        <is>
-          <t>domain:gorentals.com.pa</t>
-        </is>
-      </c>
-      <c r="B1040" t="inlineStr">
-        <is>
-          <t>gorentals.com.pa</t>
-        </is>
-      </c>
-      <c r="C1040" t="n">
-        <v>8</v>
-      </c>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>89.17.204.80</t>
-        </is>
-      </c>
-      <c r="E1040" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1040" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Panama rentals foreign; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="inlineStr">
-        <is>
-          <t>domain:greentechtree.com</t>
-        </is>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>greentechtree.com</t>
-        </is>
-      </c>
-      <c r="C1041" t="n">
-        <v>8</v>
-      </c>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>174.136.57.104</t>
-        </is>
-      </c>
-      <c r="E1041" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1041" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1041" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (generic green-tech; off-topic low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>domain:intently.co</t>
-        </is>
-      </c>
-      <c r="B1042" t="inlineStr">
-        <is>
-          <t>intently.co</t>
-        </is>
-      </c>
-      <c r="C1042" t="n">
-        <v>13</v>
-      </c>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>67.227.198.170</t>
-        </is>
-      </c>
-      <c r="E1042" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1042" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1042" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (generic off-topic; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>domain:linkcenter.com</t>
-        </is>
-      </c>
-      <c r="B1043" t="inlineStr">
-        <is>
-          <t>linkcenter.com</t>
-        </is>
-      </c>
-      <c r="C1043" t="n">
-        <v>16</v>
-      </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>78.129.199.5</t>
-        </is>
-      </c>
-      <c r="E1043" t="inlineStr">
-        <is>
-          <t>gb</t>
-        </is>
-      </c>
-      <c r="F1043" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1043" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (link-farm/directory name; link scheme)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" t="inlineStr">
-        <is>
-          <t>domain:loginslink.com</t>
-        </is>
-      </c>
-      <c r="B1044" t="inlineStr">
-        <is>
-          <t>loginslink.com</t>
-        </is>
-      </c>
-      <c r="C1044" t="n">
-        <v>24</v>
-      </c>
-      <c r="D1044" t="inlineStr">
-        <is>
-          <t>104.26.12.144</t>
-        </is>
-      </c>
-      <c r="E1044" t="inlineStr"/>
-      <c r="F1044" t="inlineStr">
-        <is>
-          <t>qa-override:known-good</t>
-        </is>
-      </c>
-      <c r="G1044" t="inlineStr">
-        <is>
-          <t>recognized legitimate platform (neutral-authority); QA agent → TOXIC (Auto-generated login-link scraper; off-topic SEO spam)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" t="inlineStr">
-        <is>
-          <t>domain:mygreenbucks.net</t>
-        </is>
-      </c>
-      <c r="B1045" t="inlineStr">
-        <is>
-          <t>mygreenbucks.net</t>
-        </is>
-      </c>
-      <c r="C1045" t="n">
-        <v>32</v>
-      </c>
-      <c r="D1045" t="inlineStr">
-        <is>
-          <t>104.21.39.229</t>
-        </is>
-      </c>
-      <c r="E1045" t="inlineStr"/>
-      <c r="F1045" t="inlineStr">
-        <is>
-          <t>qa-override:authority-no-spam</t>
-        </is>
-      </c>
-      <c r="G1045" t="inlineStr">
-        <is>
-          <t>AS&gt;=20 with no spam signal; QA agent → TOXIC (GPT/survey site)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" t="inlineStr">
-        <is>
-          <t>domain:olivare.com.ar</t>
-        </is>
-      </c>
-      <c r="B1046" t="inlineStr">
-        <is>
-          <t>olivare.com.ar</t>
-        </is>
-      </c>
-      <c r="C1046" t="n">
-        <v>13</v>
-      </c>
-      <c r="D1046" t="inlineStr">
-        <is>
-          <t>104.21.40.229</t>
-        </is>
-      </c>
-      <c r="E1046" t="inlineStr"/>
-      <c r="F1046" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1046" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Argentina one-day link; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" t="inlineStr">
-        <is>
-          <t>domain:openingtimes.co</t>
-        </is>
-      </c>
-      <c r="B1047" t="inlineStr">
-        <is>
-          <t>openingtimes.co</t>
-        </is>
-      </c>
-      <c r="C1047" t="n">
-        <v>13</v>
-      </c>
-      <c r="D1047" t="inlineStr">
-        <is>
-          <t>194.26.222.202</t>
-        </is>
-      </c>
-      <c r="E1047" t="inlineStr">
-        <is>
-          <t>gb</t>
-        </is>
-      </c>
-      <c r="F1047" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1047" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (business-hours directory aggregator; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="inlineStr">
-        <is>
-          <t>domain:pixwox.org</t>
-        </is>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t>pixwox.org</t>
-        </is>
-      </c>
-      <c r="C1048" t="n">
-        <v>16</v>
-      </c>
-      <c r="D1048" t="inlineStr">
-        <is>
-          <t>162.0.235.107</t>
-        </is>
-      </c>
-      <c r="E1048" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1048" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1048" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Instagram scraper site; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="inlineStr">
-        <is>
-          <t>domain:reputablebusinesses.com</t>
-        </is>
-      </c>
-      <c r="B1049" t="inlineStr">
-        <is>
-          <t>reputablebusinesses.com</t>
-        </is>
-      </c>
-      <c r="C1049" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1049" t="inlineStr">
-        <is>
-          <t>145.223.126.72</t>
-        </is>
-      </c>
-      <c r="E1049" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1049" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1049" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (business directory farm; one-day link)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="inlineStr">
-        <is>
-          <t>domain:resonancelabjo.com</t>
-        </is>
-      </c>
-      <c r="B1050" t="inlineStr">
-        <is>
-          <t>resonancelabjo.com</t>
-        </is>
-      </c>
-      <c r="C1050" t="n">
-        <v>13</v>
-      </c>
-      <c r="D1050" t="inlineStr">
-        <is>
-          <t>160.153.133.225</t>
-        </is>
-      </c>
-      <c r="E1050" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1050" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1050" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Jordan off-topic lab; irrelevant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="inlineStr">
-        <is>
-          <t>domain:semalt.ai</t>
-        </is>
-      </c>
-      <c r="B1051" t="inlineStr">
-        <is>
-          <t>semalt.ai</t>
-        </is>
-      </c>
-      <c r="C1051" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1051" t="inlineStr">
-        <is>
-          <t>185.100.234.251</t>
-        </is>
-      </c>
-      <c r="E1051" t="inlineStr">
-        <is>
-          <t>nl</t>
-        </is>
-      </c>
-      <c r="F1051" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1051" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (notorious spam/SEO referrer brand)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" t="inlineStr">
-        <is>
-          <t>domain:sergechel.info</t>
-        </is>
-      </c>
-      <c r="B1052" t="inlineStr">
-        <is>
-          <t>sergechel.info</t>
-        </is>
-      </c>
-      <c r="C1052" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1052" t="inlineStr">
-        <is>
-          <t>104.21.31.88</t>
-        </is>
-      </c>
-      <c r="E1052" t="inlineStr"/>
-      <c r="F1052" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1052" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (personal .info off-topic; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" t="inlineStr">
-        <is>
-          <t>domain:solvermatic.com</t>
-        </is>
-      </c>
-      <c r="B1053" t="inlineStr">
-        <is>
-          <t>solvermatic.com</t>
-        </is>
-      </c>
-      <c r="C1053" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1053" t="inlineStr">
-        <is>
-          <t>162.159.134.42</t>
-        </is>
-      </c>
-      <c r="E1053" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1053" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1053" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (generic off-topic; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1054">
-      <c r="A1054" t="inlineStr">
-        <is>
-          <t>domain:southernlanka.lk</t>
-        </is>
-      </c>
-      <c r="B1054" t="inlineStr">
-        <is>
-          <t>southernlanka.lk</t>
-        </is>
-      </c>
-      <c r="C1054" t="n">
-        <v>7</v>
-      </c>
-      <c r="D1054" t="inlineStr">
-        <is>
-          <t>135.181.210.47</t>
-        </is>
-      </c>
-      <c r="E1054" t="inlineStr">
-        <is>
-          <t>fi</t>
-        </is>
-      </c>
-      <c r="F1054" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1054" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Sri Lanka foreign; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1055">
-      <c r="A1055" t="inlineStr">
-        <is>
-          <t>domain:southfwb.com</t>
-        </is>
-      </c>
-      <c r="B1055" t="inlineStr">
-        <is>
-          <t>southfwb.com</t>
-        </is>
-      </c>
-      <c r="C1055" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1055" t="inlineStr">
-        <is>
-          <t>104.21.16.20</t>
-        </is>
-      </c>
-      <c r="E1055" t="inlineStr"/>
-      <c r="F1055" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1055" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (generic name; one-day low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" t="inlineStr">
-        <is>
-          <t>domain:sportmediaset.co</t>
-        </is>
-      </c>
-      <c r="B1056" t="inlineStr">
-        <is>
-          <t>sportmediaset.co</t>
-        </is>
-      </c>
-      <c r="C1056" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1056" t="inlineStr">
-        <is>
-          <t>172.67.192.199</t>
-        </is>
-      </c>
-      <c r="E1056" t="inlineStr"/>
-      <c r="F1056" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1056" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Mediaset sport typo; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" t="inlineStr">
-        <is>
-          <t>domain:swipenow.com</t>
-        </is>
-      </c>
-      <c r="B1057" t="inlineStr">
-        <is>
-          <t>swipenow.com</t>
-        </is>
-      </c>
-      <c r="C1057" t="n">
-        <v>9</v>
-      </c>
-      <c r="D1057" t="inlineStr">
-        <is>
-          <t>148.72.27.147</t>
-        </is>
-      </c>
-      <c r="E1057" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1057" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1057" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (generic app off-topic; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" t="inlineStr">
-        <is>
-          <t>domain:thenllc.ca</t>
-        </is>
-      </c>
-      <c r="B1058" t="inlineStr">
-        <is>
-          <t>thenllc.ca</t>
-        </is>
-      </c>
-      <c r="C1058" t="n">
-        <v>10</v>
-      </c>
-      <c r="D1058" t="inlineStr">
-        <is>
-          <t>156.67.77.68</t>
-        </is>
-      </c>
-      <c r="E1058" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1058" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1058" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (generic LLC Canada; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1059">
-      <c r="A1059" t="inlineStr">
-        <is>
-          <t>domain:thesocialhouseja.com</t>
-        </is>
-      </c>
-      <c r="B1059" t="inlineStr">
-        <is>
-          <t>thesocialhouseja.com</t>
-        </is>
-      </c>
-      <c r="C1059" t="n">
-        <v>7</v>
-      </c>
-      <c r="D1059" t="inlineStr">
-        <is>
-          <t>72.167.69.37</t>
-        </is>
-      </c>
-      <c r="E1059" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1059" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1059" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (Jamaica social off-topic; low authority)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1060">
-      <c r="A1060" t="inlineStr">
-        <is>
-          <t>domain:vangvela.com</t>
-        </is>
-      </c>
-      <c r="B1060" t="inlineStr">
-        <is>
-          <t>vangvela.com</t>
-        </is>
-      </c>
-      <c r="C1060" t="n">
-        <v>16</v>
-      </c>
-      <c r="D1060" t="inlineStr">
-        <is>
-          <t>195.35.60.128</t>
-        </is>
-      </c>
-      <c r="E1060" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1060" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1060" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (nonsense name off-topic; AS16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1061">
-      <c r="A1061" t="inlineStr">
-        <is>
-          <t>domain:viral-status.com</t>
-        </is>
-      </c>
-      <c r="B1061" t="inlineStr">
-        <is>
-          <t>viral-status.com</t>
-        </is>
-      </c>
-      <c r="C1061" t="n">
-        <v>18</v>
-      </c>
-      <c r="D1061" t="inlineStr">
-        <is>
-          <t>104.21.72.65</t>
-        </is>
-      </c>
-      <c r="E1061" t="inlineStr"/>
-      <c r="F1061" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1061" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (viral-content farm; off-topic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" t="inlineStr">
-        <is>
-          <t>domain:wealthyoverview.com</t>
-        </is>
-      </c>
-      <c r="B1062" t="inlineStr">
-        <is>
-          <t>wealthyoverview.com</t>
-        </is>
-      </c>
-      <c r="C1062" t="n">
-        <v>7</v>
-      </c>
-      <c r="D1062" t="inlineStr">
-        <is>
-          <t>172.67.130.236</t>
-        </is>
-      </c>
-      <c r="E1062" t="inlineStr"/>
-      <c r="F1062" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1062" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (finance off-topic content; AS7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" t="inlineStr">
-        <is>
-          <t>domain:websitescrawl.com</t>
-        </is>
-      </c>
-      <c r="B1063" t="inlineStr">
-        <is>
-          <t>websitescrawl.com</t>
-        </is>
-      </c>
-      <c r="C1063" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1063" t="inlineStr">
-        <is>
-          <t>68.178.235.175</t>
-        </is>
-      </c>
-      <c r="E1063" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F1063" t="inlineStr">
-        <is>
-          <t>qa-override:unclassified</t>
-        </is>
-      </c>
-      <c r="G1063" t="inlineStr">
-        <is>
-          <t>no strong signal — human QA; QA agent → TOXIC (crawler/directory SEO name; link scheme)</t>
+          <t>no strong signal — human QA; QA agent → TOXIC (SEO crawler-style tool name no value)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G1063"/>
+  <autoFilter ref="A5:G1009"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
